--- a/数据.xlsx
+++ b/数据.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D2:K101"/>
+  <dimension ref="A2:K125"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" style="9" min="1" max="1"/>
@@ -671,684 +671,700 @@
         <v>0.22</v>
       </c>
     </row>
+    <row r="11">
+      <c r="E11" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.295</v>
+      </c>
+    </row>
     <row r="12">
-      <c r="D12" s="8" t="inlineStr">
+      <c r="E12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.355</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>SE-PreResNet-110</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G14" s="3" t="n">
         <v>0.045</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>0.295</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I14" s="3" t="n">
         <v>0.305</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J14" s="3" t="n">
         <v>0.39</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K14" s="3" t="n">
         <v>0.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="E13" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0.315</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.265</v>
       </c>
     </row>
     <row r="15" s="9">
       <c r="E15" s="3" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.21</v>
+        <v>0.255</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.065</v>
+        <v>0.045</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.2</v>
+        <v>0.295</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.195</v>
+        <v>0.28</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.225</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="16" s="9">
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.18</v>
+        <v>0.245</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.145</v>
+        <v>0.225</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.215</v>
+        <v>0.255</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.205</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="17">
       <c r="E17" s="3" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.045</v>
+        <v>0.065</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.185</v>
+        <v>0.2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.13</v>
+        <v>0.195</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.195</v>
+        <v>0.23</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.205</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.205</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.205</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>0.165</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>0.045</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>0.185</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>0.175</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K20" s="3" t="n">
         <v>0.225</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>SE-ResNet-20</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>MIFGSM</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.355</v>
       </c>
     </row>
     <row r="21" s="9">
       <c r="E21" s="3" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.19</v>
+        <v>0.185</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.235</v>
+        <v>0.05</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.165</v>
+        <v>0.185</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.28</v>
+        <v>0.295</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.265</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="22" s="9">
       <c r="E22" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.15</v>
+        <v>0.265</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.17</v>
+        <v>0.055</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.035</v>
+        <v>0.235</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.14</v>
+        <v>0.245</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="E23" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H23" s="3" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="I23" s="3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.165</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="E24" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>0.025</v>
-      </c>
       <c r="I24" s="3" t="n">
-        <v>0.13</v>
+        <v>0.245</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.175</v>
+        <v>0.355</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.18</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="25">
       <c r="E25" s="3" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.145</v>
+        <v>0.19</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.18</v>
+        <v>0.235</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.15</v>
+        <v>0.165</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.21</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="26">
       <c r="E26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.215</v>
+        <v>0.17</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.14</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.245</v>
-      </c>
-    </row>
-    <row r="27" s="9"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" s="9">
+      <c r="E27" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.165</v>
+      </c>
+    </row>
     <row r="28" s="9">
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>DenseNet-BC-40</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>MIFGSM</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.385</v>
+        <v>0.135</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.445</v>
+        <v>0.18</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.435</v>
+        <v>0.025</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.015</v>
+        <v>0.13</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.52</v>
+        <v>0.175</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="29">
       <c r="E29" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.3</v>
+        <v>0.145</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.285</v>
+        <v>0.025</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.425</v>
+        <v>0.23</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="30">
       <c r="E30" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.34</v>
+        <v>0.215</v>
       </c>
       <c r="H30" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="I30" s="3" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0.35</v>
-      </c>
       <c r="K30" s="3" t="n">
-        <v>0.355</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="31">
       <c r="E31" s="3" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.21</v>
+        <v>0.195</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.235</v>
+        <v>0.015</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.075</v>
+        <v>0.165</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="32">
       <c r="E32" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.195</v>
+        <v>0.265</v>
       </c>
       <c r="G32" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="33" s="9"/>
+    <row r="34" s="9">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>0.285</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0.335</v>
-      </c>
-    </row>
-    <row r="33" s="9">
-      <c r="E33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="I35" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>0.355</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>0.335</v>
-      </c>
-    </row>
-    <row r="34" s="9">
-      <c r="E34" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0.385</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>RoR-3-110</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>MIFGSM</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0.51</v>
       </c>
     </row>
     <row r="37">
       <c r="E37" s="3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.415</v>
+        <v>0.235</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.38</v>
+        <v>0.075</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.025</v>
+        <v>0.28</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0.46</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="38">
       <c r="E38" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="3" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="K38" s="3" t="n">
         <v>0.335</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0.37</v>
       </c>
     </row>
     <row r="39" s="9">
       <c r="E39" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.305</v>
+        <v>0.215</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.315</v>
+        <v>0.23</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.28</v>
+        <v>0.04</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.325</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="40" s="9">
       <c r="E40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.27</v>
+        <v>0.295</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.325</v>
+        <v>0.41</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.305</v>
+        <v>0.32</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.245</v>
+        <v>0.02</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.125</v>
+        <v>0.41</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.31</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="41">
       <c r="E41" s="3" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.225</v>
+        <v>0.48</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.3</v>
+        <v>0.535</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.265</v>
+        <v>0.415</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.215</v>
+        <v>0.02</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.095</v>
+        <v>0.57</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.275</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="42">
       <c r="E42" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.21</v>
+        <v>0.555</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.26</v>
+        <v>0.64</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.24</v>
+        <v>0.555</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.22</v>
+        <v>0.025</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.615</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.265</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" s="9"/>
     <row r="44">
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>DIA-PreResNet-56</t>
+          <t>RoR-3-110</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1357,22 +1373,22 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.445</v>
+        <v>0.425</v>
       </c>
       <c r="G44" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>0.435</v>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>0.46</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.495</v>
+        <v>0.03</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.195</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="45">
@@ -1380,22 +1396,22 @@
         <v>0.5</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.435</v>
+        <v>0.42</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0.43</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.445</v>
+        <v>0.415</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.465</v>
+        <v>0.025</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="46">
@@ -1403,22 +1419,22 @@
         <v>1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.43</v>
+        <v>0.335</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.445</v>
+        <v>0.35</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.445</v>
+        <v>0.275</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.47</v>
+        <v>0.065</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.265</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="47">
@@ -1426,22 +1442,22 @@
         <v>1.5</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.36</v>
+        <v>0.305</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.36</v>
+        <v>0.315</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.385</v>
+        <v>0.12</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.225</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="48">
@@ -1449,22 +1465,22 @@
         <v>2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.295</v>
+        <v>0.325</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.3</v>
+        <v>0.305</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.295</v>
+        <v>0.245</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.32</v>
+        <v>0.125</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.195</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="49" s="9">
@@ -1472,22 +1488,22 @@
         <v>2.5</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.24</v>
+        <v>0.225</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.26</v>
+        <v>0.265</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.265</v>
+        <v>0.215</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.27</v>
+        <v>0.095</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.175</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="50" s="9">
@@ -1495,751 +1511,765 @@
         <v>3</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G50" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K50" s="3" t="n">
         <v>0.265</v>
       </c>
-      <c r="H50" s="3" t="n">
+    </row>
+    <row r="51">
+      <c r="E51" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F51" s="3" t="n">
         <v>0.22</v>
       </c>
-      <c r="I50" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>黑盒攻击损失值（越大攻击效果越好）(N=5)</t>
-        </is>
+      <c r="G51" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0.305</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="54">
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>代理模型</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>beta</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>ResNet-5</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>SE-PreResNet-110</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>SE-ResNet-20</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>DenseNet-BC-40（k=12）</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>RoR-3-110</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>DIA-PreResNet-56</t>
         </is>
       </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.195</v>
+      </c>
     </row>
     <row r="55" s="9">
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>ResNet-56</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>MIFGSM</t>
-        </is>
+      <c r="E55" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>9.960459999999999</v>
+        <v>0.435</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2.63602</v>
+        <v>0.43</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>2.93902</v>
+        <v>0.445</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>3.5534</v>
+        <v>0.44</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>2.4141</v>
+        <v>0.465</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>3.18371</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="56" s="9">
       <c r="E56" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>9.156409999999999</v>
+        <v>0.43</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.89706</v>
+        <v>0.45</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>3.42002</v>
+        <v>0.445</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>4.01273</v>
+        <v>0.445</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>2.78511</v>
+        <v>0.47</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>3.53974</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>7.97424</v>
+        <v>0.36</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>2.97441</v>
+        <v>0.37</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>3.91685</v>
+        <v>0.36</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>4.13877</v>
+        <v>0.36</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>2.87134</v>
+        <v>0.385</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>3.97842</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>7.44392</v>
+        <v>0.29</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>2.98016</v>
+        <v>0.295</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>4.24909</v>
+        <v>0.3</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>4.25111</v>
+        <v>0.295</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>2.92426</v>
+        <v>0.32</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>4.36281</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="59">
       <c r="E59" s="3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>7.17928</v>
+        <v>0.24</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2.95681</v>
+        <v>0.25</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>4.43675</v>
+        <v>0.26</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>4.33715</v>
+        <v>0.265</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>2.90341</v>
+        <v>0.27</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>4.56025</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>7.59767</v>
+        <v>0.23</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>2.8952</v>
+        <v>0.265</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>4.40358</v>
+        <v>0.22</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>4.35279</v>
+        <v>0.23</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>2.83398</v>
+        <v>0.26</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>4.4333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="61" s="9">
       <c r="E61" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>7.80579</v>
+        <v>0.215</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2.69823</v>
+        <v>0.29</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>4.08547</v>
+        <v>0.205</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>4.17524</v>
+        <v>0.23</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2.65719</v>
+        <v>0.26</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>4.14313</v>
-      </c>
-    </row>
-    <row r="62" s="9"/>
-    <row r="63">
-      <c r="D63" s="8" t="inlineStr">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="62" s="9">
+      <c r="E62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>黑盒攻击损失值（越大攻击效果越好）(N=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>代理模型</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>ResNet-5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>SE-PreResNet-110</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40（k=12）</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" s="9">
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>ResNet-56</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>4.38148</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>9.95201</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>3.37386</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>3.81884</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>2.80962</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>3.47645</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="E64" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>4.81055</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>8.91596</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>3.73428</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>4.23355</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>3.18687</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>4.2622</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="E65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>5.09863</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>7.66787</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>4.25727</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>4.46174</v>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>3.46495</v>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>4.70913</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="E66" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>5.50833</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>6.76992</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>4.44884</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>4.65787</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>3.49636</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>4.92523</v>
-      </c>
-    </row>
-    <row r="67" s="9">
-      <c r="E67" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="F67" s="3" t="n">
-        <v>5.64218</v>
+        <v>9.960459999999999</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>6.24152</v>
+        <v>2.63602</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>4.5398</v>
+        <v>2.93902</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>4.63838</v>
+        <v>3.5534</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>3.4174</v>
+        <v>2.4141</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>4.88161</v>
+        <v>3.18371</v>
       </c>
     </row>
     <row r="68" s="9">
       <c r="E68" s="3" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>5.83259</v>
+        <v>9.156409999999999</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>5.67627</v>
+        <v>2.89706</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>4.46957</v>
+        <v>3.42002</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>4.67463</v>
+        <v>4.01273</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>3.3086</v>
+        <v>2.78511</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>4.82279</v>
+        <v>3.53974</v>
       </c>
     </row>
     <row r="69">
       <c r="E69" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>5.48806</v>
+        <v>7.97424</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>5.30967</v>
+        <v>2.97441</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>4.19472</v>
+        <v>3.91685</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>4.41523</v>
+        <v>4.13877</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>2.99933</v>
+        <v>2.87134</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>4.45001</v>
+        <v>3.97842</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="E70" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>7.44392</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>2.98016</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>4.24909</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>4.25111</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>2.92426</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>4.36281</v>
       </c>
     </row>
     <row r="71">
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>SE-ResNet-20</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>MIFGSM</t>
-        </is>
+      <c r="E71" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>4.43778</v>
+        <v>7.17928</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.68155</v>
+        <v>2.95681</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>12.39732</v>
+        <v>4.43675</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>3.80847</v>
+        <v>4.33715</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.39275</v>
+        <v>2.90341</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>3.38826</v>
+        <v>4.56025</v>
       </c>
     </row>
     <row r="72">
       <c r="E72" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>5.41744</v>
+        <v>7.59767</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3.12383</v>
+        <v>2.8952</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11.94849</v>
+        <v>4.40358</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>4.54404</v>
+        <v>4.35279</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2.75929</v>
+        <v>2.83398</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>4.11948</v>
+        <v>4.4333</v>
       </c>
     </row>
     <row r="73" s="9">
       <c r="E73" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>6.09906</v>
+        <v>7.80579</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>3.48682</v>
+        <v>2.69823</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>10.33462</v>
+        <v>4.08547</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>5.13824</v>
+        <v>4.17524</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>3.07726</v>
+        <v>2.65719</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>4.63591</v>
+        <v>4.14313</v>
       </c>
     </row>
     <row r="74" s="9">
       <c r="E74" s="3" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>6.43411</v>
+        <v>7.88552</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>3.57374</v>
+        <v>2.35188</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>9.13749</v>
+        <v>3.40819</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>5.21115</v>
+        <v>3.81749</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>3.21733</v>
+        <v>2.39622</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>4.99159</v>
+        <v>3.52071</v>
       </c>
     </row>
     <row r="75">
       <c r="E75" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>6.18764</v>
+        <v>7.83443</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3.35431</v>
+        <v>1.99529</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>8.50858</v>
+        <v>2.83184</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>5.11119</v>
+        <v>3.23933</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>3.06766</v>
+        <v>1.8864</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>4.70662</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="E76" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>5.96045</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>3.22363</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>8.05494</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>4.9347</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>2.83232</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>4.49893</v>
+        <v>2.79115</v>
       </c>
     </row>
     <row r="77">
-      <c r="E77" s="3" t="n">
-        <v>3</v>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>5.53402</v>
+        <v>4.38148</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2.91705</v>
+        <v>9.95201</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>7.75801</v>
+        <v>3.37386</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>4.62243</v>
+        <v>3.81884</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2.54868</v>
+        <v>2.80962</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>4.07519</v>
-      </c>
-    </row>
-    <row r="78" s="9"/>
+        <v>3.47645</v>
+      </c>
+    </row>
+    <row r="78" s="9">
+      <c r="E78" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>4.81055</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>8.91596</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>3.73428</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>4.23355</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>3.18687</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>4.2622</v>
+      </c>
+    </row>
     <row r="79" s="9">
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>DenseNet-BC-40</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>MIFGSM</t>
-        </is>
+      <c r="E79" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>3.3188</v>
+        <v>5.09863</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2.11657</v>
+        <v>7.66787</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2.38242</v>
+        <v>4.25727</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>12.50286</v>
+        <v>4.46174</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>1.72487</v>
+        <v>3.46495</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>2.24107</v>
+        <v>4.70913</v>
       </c>
     </row>
     <row r="80" s="9">
       <c r="E80" s="3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>4.2457</v>
+        <v>5.50833</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.57025</v>
+        <v>6.76992</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>3.22984</v>
+        <v>4.44884</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>11.71959</v>
+        <v>4.65787</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>2.23699</v>
+        <v>3.49636</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>3.02985</v>
+        <v>4.92523</v>
       </c>
     </row>
     <row r="81">
       <c r="E81" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>4.7004</v>
+        <v>5.64218</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2.82025</v>
+        <v>6.24152</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>3.63166</v>
+        <v>4.5398</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>10.07037</v>
+        <v>4.63838</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>2.56895</v>
+        <v>3.4174</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>3.44993</v>
+        <v>4.88161</v>
       </c>
     </row>
     <row r="82">
       <c r="E82" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>5.17196</v>
+        <v>5.83259</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>2.87551</v>
+        <v>5.67627</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>4.07888</v>
+        <v>4.46957</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>8.802149999999999</v>
+        <v>4.67463</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2.68939</v>
+        <v>3.3086</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>3.79773</v>
+        <v>4.82279</v>
       </c>
     </row>
     <row r="83">
       <c r="E83" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>5.20782</v>
+        <v>5.48806</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2.73591</v>
+        <v>5.30967</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>3.98449</v>
+        <v>4.19472</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>8.07826</v>
+        <v>4.41523</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>2.56269</v>
+        <v>2.99933</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>3.50999</v>
+        <v>4.45001</v>
       </c>
     </row>
     <row r="84">
       <c r="E84" s="3" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>4.59611</v>
+        <v>4.85567</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.42815</v>
+        <v>5.0115</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>3.67429</v>
+        <v>3.79124</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>7.84998</v>
+        <v>4.00274</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>2.40956</v>
+        <v>2.60281</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>3.25457</v>
+        <v>4.09592</v>
       </c>
     </row>
     <row r="85">
       <c r="E85" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>3.78133</v>
+        <v>4.16081</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1.99764</v>
+        <v>4.72852</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2.91753</v>
+        <v>3.27898</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>7.69562</v>
+        <v>3.54386</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>1.99797</v>
+        <v>2.27349</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>2.7406</v>
+        <v>3.42237</v>
       </c>
     </row>
     <row r="87">
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>RoR-3-110</t>
+          <t>SE-ResNet-20</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2248,22 +2278,22 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>3.49242</v>
+        <v>4.43778</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>2.45597</v>
+        <v>2.68155</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>2.45505</v>
+        <v>12.39732</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>3.04778</v>
+        <v>3.80847</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>7.06688</v>
+        <v>2.39275</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>2.72461</v>
+        <v>3.38826</v>
       </c>
     </row>
     <row r="88">
@@ -2271,22 +2301,22 @@
         <v>0.5</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>3.77323</v>
+        <v>5.41744</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2.74622</v>
+        <v>3.12383</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2.74619</v>
+        <v>11.94849</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>3.35825</v>
+        <v>4.54404</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>6.34906</v>
+        <v>2.75929</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>3.10186</v>
+        <v>4.11948</v>
       </c>
     </row>
     <row r="89">
@@ -2294,22 +2324,22 @@
         <v>1</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>4.55179</v>
+        <v>6.09906</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>3.1279</v>
+        <v>3.48682</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>3.51447</v>
+        <v>10.33462</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>3.90468</v>
+        <v>5.13824</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>5.54531</v>
+        <v>3.07726</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>3.67123</v>
+        <v>4.63591</v>
       </c>
     </row>
     <row r="90">
@@ -2317,22 +2347,22 @@
         <v>1.5</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>4.66683</v>
+        <v>6.43411</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>3.12799</v>
+        <v>3.57374</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>3.68091</v>
+        <v>9.13749</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>3.91165</v>
+        <v>5.21115</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>4.81146</v>
+        <v>3.21733</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>4.07802</v>
+        <v>4.99159</v>
       </c>
     </row>
     <row r="91">
@@ -2340,22 +2370,22 @@
         <v>2</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>4.86752</v>
+        <v>6.18764</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>3.08449</v>
+        <v>3.35431</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>3.85941</v>
+        <v>8.50858</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>3.97265</v>
+        <v>5.11119</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>4.53676</v>
+        <v>3.06766</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>4.13842</v>
+        <v>4.70662</v>
       </c>
     </row>
     <row r="92">
@@ -2363,22 +2393,22 @@
         <v>2.5</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>5.215</v>
+        <v>5.96045</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3.02471</v>
+        <v>3.22363</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>3.89843</v>
+        <v>8.05494</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>4.05517</v>
+        <v>4.9347</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>4.30283</v>
+        <v>2.83232</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>4.20544</v>
+        <v>4.49893</v>
       </c>
     </row>
     <row r="93">
@@ -2386,206 +2416,726 @@
         <v>3</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>5.22394</v>
+        <v>5.53402</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2.91395</v>
+        <v>2.91705</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>3.82372</v>
+        <v>7.75801</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>3.90048</v>
+        <v>4.62243</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>4.22289</v>
+        <v>2.54868</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>4.14564</v>
+        <v>4.07519</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="E94" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>5.02015</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>2.65018</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>7.48808</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>4.3855</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>2.25553</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>3.67838</v>
       </c>
     </row>
     <row r="95">
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>DIA-PreResNet-56</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E95" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>4.2279</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>2.39785</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>7.15877</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>3.86667</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>1.97705</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>3.16152</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F95" s="3" t="n">
-        <v>3.25545</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>2.40469</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>2.30561</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>2.59116</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>2.06655</v>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>7.09179</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="E96" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>3.33047</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>2.61097</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>2.66209</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>2.92741</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>2.25123</v>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>6.73145</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="E97" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="F97" s="3" t="n">
-        <v>3.50584</v>
+        <v>3.3188</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>2.63476</v>
+        <v>2.11657</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>2.69106</v>
+        <v>2.38242</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>2.90856</v>
+        <v>12.50286</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>2.32654</v>
+        <v>1.72487</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>6.02728</v>
+        <v>2.24107</v>
       </c>
     </row>
     <row r="98">
       <c r="E98" s="3" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>4.54736</v>
+        <v>4.2457</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>3.05303</v>
+        <v>2.57025</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>3.42126</v>
+        <v>3.22984</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>3.5237</v>
+        <v>11.71959</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>2.72446</v>
+        <v>2.23699</v>
       </c>
       <c r="K98" s="3" t="n">
-        <v>6.30271</v>
+        <v>3.02985</v>
       </c>
     </row>
     <row r="99">
       <c r="E99" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>5.00058</v>
+        <v>4.7004</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3.17491</v>
+        <v>2.82025</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>3.91396</v>
+        <v>3.63166</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>3.87685</v>
+        <v>10.07037</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>2.86181</v>
+        <v>2.56895</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>6.39424</v>
+        <v>3.44993</v>
       </c>
     </row>
     <row r="100">
       <c r="E100" s="3" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>5.40266</v>
+        <v>5.17196</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>3.1888</v>
+        <v>2.87551</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>4.0229</v>
+        <v>4.07888</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>3.90637</v>
+        <v>8.802149999999999</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>2.93938</v>
+        <v>2.68939</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>6.43327</v>
+        <v>3.79773</v>
       </c>
     </row>
     <row r="101">
       <c r="E101" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>5.20782</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>2.73591</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>3.98449</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>8.07826</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>2.56269</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>3.50999</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="E102" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>4.59611</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>2.42815</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>3.67429</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>7.84998</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>2.40956</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>3.25457</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F101" s="3" t="n">
+      <c r="F103" s="3" t="n">
+        <v>3.78133</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>1.99764</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>2.91753</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>7.69562</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>1.99797</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>2.7406</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="E104" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>2.69167</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>1.57072</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>2.2805</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>7.40605</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>1.43429</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>2.0703</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="E105" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>2.03654</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>1.26738</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>1.71211</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>7.0514</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>1.16237</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>1.57665</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>3.49242</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>2.45597</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>2.45505</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>3.04778</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>7.06688</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>2.72461</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="E108" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>3.77323</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>2.74622</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>2.74619</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>3.35825</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>6.34906</v>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>3.10186</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>4.55179</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>3.1279</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>3.51447</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>3.90468</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>5.54531</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>3.67123</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="E110" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>4.66683</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>3.12799</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>3.68091</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>3.91165</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>4.81146</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>4.07802</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="E111" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>4.86752</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>3.08449</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>3.85941</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>3.97265</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>4.53676</v>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>4.13842</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="E112" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>5.215</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>3.02471</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>3.89843</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>4.05517</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>4.30283</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>4.20544</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="E113" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>5.22394</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>2.91395</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>3.82372</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>3.90048</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>4.22289</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>4.14564</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="E114" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>4.88615</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>2.68523</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>3.5826</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>3.65424</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>4.11785</v>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>3.67876</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="E115" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>4.45347</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>2.40058</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>3.18861</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>3.46411</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>4.0787</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>3.13743</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>3.25545</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>2.40469</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>2.30561</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>2.59116</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>2.06655</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>7.09179</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="E118" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>3.33047</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>2.61097</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>2.66209</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>2.92741</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>2.25123</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>6.73145</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="E119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>3.50584</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>2.63476</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>2.69106</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>2.90856</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>2.32654</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>6.02728</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="E120" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>4.54736</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>3.05303</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>3.42126</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>3.5237</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>2.72446</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>6.30271</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="E121" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>5.00058</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>3.17491</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>3.91396</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>3.87685</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>2.86181</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>6.39424</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="E122" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>5.40266</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>3.1888</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>4.0229</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>3.90637</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>2.93938</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>6.43327</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="E123" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" s="3" t="n">
         <v>5.32115</v>
       </c>
-      <c r="G101" s="3" t="n">
+      <c r="G123" s="3" t="n">
         <v>3.01057</v>
       </c>
-      <c r="H101" s="3" t="n">
+      <c r="H123" s="3" t="n">
         <v>4.00404</v>
       </c>
-      <c r="I101" s="3" t="n">
+      <c r="I123" s="3" t="n">
         <v>3.89982</v>
       </c>
-      <c r="J101" s="3" t="n">
+      <c r="J123" s="3" t="n">
         <v>2.7541</v>
       </c>
-      <c r="K101" s="3" t="n">
+      <c r="K123" s="3" t="n">
         <v>6.51448</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="E124" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>5.06484</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>2.7978</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>3.76481</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>3.76457</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>6.57915</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="E125" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>4.53192</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>2.45848</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>3.39727</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>3.45727</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>2.27774</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>6.45521</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="D71:D77"/>
-    <mergeCell ref="D63:D69"/>
-    <mergeCell ref="D79:D85"/>
-    <mergeCell ref="D95:D101"/>
-    <mergeCell ref="D87:D93"/>
-    <mergeCell ref="D28:D34"/>
-    <mergeCell ref="D44:D50"/>
-    <mergeCell ref="D4:D10"/>
-    <mergeCell ref="D55:D61"/>
-    <mergeCell ref="D12:D18"/>
-    <mergeCell ref="D20:D26"/>
-    <mergeCell ref="D36:D42"/>
+    <mergeCell ref="D14:D22"/>
+    <mergeCell ref="D44:D52"/>
+    <mergeCell ref="D4:D12"/>
+    <mergeCell ref="D67:D75"/>
+    <mergeCell ref="D77:D85"/>
+    <mergeCell ref="D117:D125"/>
+    <mergeCell ref="D107:D115"/>
+    <mergeCell ref="D34:D42"/>
+    <mergeCell ref="D54:D62"/>
+    <mergeCell ref="D87:D95"/>
+    <mergeCell ref="D24:D32"/>
+    <mergeCell ref="D97:D105"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/数据.xlsx
+++ b/数据.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -45,13 +45,6 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -75,11 +68,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -88,26 +78,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -438,2704 +416,6425 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:K125"/>
+  <dimension ref="D1:AE130"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="13" customWidth="1" style="9" min="1" max="1"/>
-    <col width="13" customWidth="1" style="9" min="2" max="2"/>
-    <col width="13" customWidth="1" style="9" min="3" max="3"/>
-    <col width="13" customWidth="1" style="9" min="4" max="4"/>
-    <col width="13" customWidth="1" style="9" min="5" max="5"/>
-    <col width="13" customWidth="1" style="9" min="6" max="6"/>
-    <col width="13" customWidth="1" style="9" min="7" max="7"/>
-    <col width="13" customWidth="1" style="9" min="8" max="8"/>
-    <col width="13" customWidth="1" style="9" min="9" max="9"/>
-    <col width="13" customWidth="1" style="9" min="10" max="10"/>
-    <col width="13" customWidth="1" style="9" min="11" max="11"/>
+    <col width="13" customWidth="1" style="6" min="1" max="11"/>
+    <col width="13" customWidth="1" style="6" min="14" max="21"/>
+    <col width="13" customWidth="1" style="6" min="24" max="24"/>
+    <col width="13" customWidth="1" style="6" min="25" max="25"/>
+    <col width="13" customWidth="1" style="6" min="26" max="26"/>
+    <col width="13" customWidth="1" style="6" min="27" max="27"/>
+    <col width="13" customWidth="1" style="6" min="28" max="28"/>
+    <col width="13" customWidth="1" style="6" min="29" max="29"/>
+    <col width="13" customWidth="1" style="6" min="30" max="30"/>
+    <col width="13" customWidth="1" style="6" min="31" max="31"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="F2" s="11" t="inlineStr">
+    <row r="1">
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="72" customHeight="1" s="6">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>噪声强度影响准确率（越小攻击效果越好）(N=5)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" s="9">
-      <c r="D3" s="2" t="inlineStr">
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>邻域样本数影响准确率（越小攻击效果越好）(beta=2.5)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="n"/>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>不同攻击方法影响准确率（越小攻击效果越好）</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="n"/>
+      <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="n"/>
+      <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="6">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>代理模型</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>ResNet-5</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>SE-PreResNet-110</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>SE-ResNet-20</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>DenseNet-BC-40（k=12）</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>RoR-3-110</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>DIA-PreResNet-56</t>
         </is>
       </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>代理模型</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>ResNet-5</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40（k=12）</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>代理模型</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="Z3" s="1" t="inlineStr">
+        <is>
+          <t>ResNet-5</t>
+        </is>
+      </c>
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="AB3" s="1" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40（k=12）</t>
+        </is>
+      </c>
+      <c r="AC3" s="1" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40?k=12?</t>
+        </is>
+      </c>
+      <c r="AD3" s="1" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="AE3" s="1" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>ResNet-56</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.37</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.345</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="2" t="n">
         <v>0.335</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="2" t="n">
         <v>0.37</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.42</v>
       </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>ResNet-56</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>ResNet-56</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="5">
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.315</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="2" t="n">
         <v>0.315</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="2" t="n">
         <v>0.345</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.38</v>
       </c>
+      <c r="O5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD5" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AE5" s="2" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="6">
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="2" t="n">
         <v>0.135</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="2" t="n">
         <v>0.265</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.34</v>
       </c>
+      <c r="O6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="7">
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="2" t="n">
         <v>0.24</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.275</v>
       </c>
+      <c r="O7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X7" s="2" t="n"/>
+      <c r="Y7" s="2" t="n"/>
+      <c r="Z7" s="2" t="n"/>
+      <c r="AA7" s="2" t="n"/>
+      <c r="AB7" s="2" t="n"/>
+      <c r="AC7" s="2" t="n"/>
+      <c r="AD7" s="2" t="n"/>
+      <c r="AE7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="2" t="n">
         <v>0.175</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="2" t="n">
         <v>0.225</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="9" s="9">
-      <c r="E9" s="3" t="n">
+      <c r="O8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X8" s="5" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="E9" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="2" t="n">
         <v>0.115</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.17</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="10" s="9">
-      <c r="E10" s="3" t="n">
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="n"/>
+      <c r="U9" s="2" t="n"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="2" t="n">
         <v>0.065</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="2" t="n">
         <v>0.19</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="2" t="n">
         <v>0.245</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>0.22</v>
       </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="11">
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="2" t="n">
         <v>0.315</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>0.295</v>
       </c>
+      <c r="O11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
+      <c r="AA11" s="2" t="n"/>
+      <c r="AB11" s="2" t="n"/>
+      <c r="AC11" s="2" t="n"/>
+      <c r="AD11" s="2" t="n"/>
+      <c r="AE11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="2" t="n">
         <v>0.025</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="2" t="n">
         <v>0.395</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.315</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="2" t="n">
         <v>0.395</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>0.355</v>
       </c>
+      <c r="O12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X12" s="5" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="O13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
     </row>
     <row r="14">
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>SE-PreResNet-110</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.295</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="2" t="n">
         <v>0.305</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="15" s="9">
-      <c r="E15" s="3" t="n">
+      <c r="O14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>0.355</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="2" t="n">
         <v>0.255</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="2" t="n">
         <v>0.295</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="2" t="n">
         <v>0.32</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>0.315</v>
       </c>
-    </row>
-    <row r="16" s="9">
-      <c r="E16" s="3" t="n">
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n"/>
+      <c r="U15" s="2" t="n"/>
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="2" t="n"/>
+      <c r="Z15" s="2" t="n"/>
+      <c r="AA15" s="2" t="n"/>
+      <c r="AB15" s="2" t="n"/>
+      <c r="AC15" s="2" t="n"/>
+      <c r="AD15" s="2" t="n"/>
+      <c r="AE15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="2" t="n">
         <v>0.245</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" s="2" t="n">
         <v>0.225</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" s="2" t="n">
         <v>0.255</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>0.265</v>
       </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="AB16" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="17">
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="2" t="n">
         <v>0.065</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" s="2" t="n">
         <v>0.195</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J17" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>0.225</v>
       </c>
+      <c r="O17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>0.74</v>
+      </c>
     </row>
     <row r="18">
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="2" t="n">
         <v>0.06</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="2" t="n">
         <v>0.145</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J18" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>0.205</v>
       </c>
+      <c r="O18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AB18" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>0.52</v>
+      </c>
     </row>
     <row r="19">
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="2" t="n">
         <v>0.185</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="J19" s="2" t="n">
         <v>0.195</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>0.205</v>
       </c>
+      <c r="O19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X19" s="2" t="n"/>
+      <c r="Y19" s="2" t="n"/>
+      <c r="Z19" s="2" t="n"/>
+      <c r="AA19" s="2" t="n"/>
+      <c r="AB19" s="2" t="n"/>
+      <c r="AC19" s="2" t="n"/>
+      <c r="AD19" s="2" t="n"/>
+      <c r="AE19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="2" t="n">
         <v>0.165</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="2" t="n">
         <v>0.185</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="2" t="n">
         <v>0.175</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J20" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>0.225</v>
       </c>
-    </row>
-    <row r="21" s="9">
-      <c r="E21" s="3" t="n">
+      <c r="O20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="X20" s="5" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="AB20" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>0.655</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="2" t="n">
         <v>0.185</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="2" t="n">
         <v>0.185</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="J21" s="2" t="n">
         <v>0.295</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="22" s="9">
-      <c r="E22" s="3" t="n">
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AB21" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>0.695</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="2" t="n">
         <v>0.265</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="2" t="n">
         <v>0.055</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" s="2" t="n">
         <v>0.235</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" s="2" t="n">
         <v>0.245</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>0.31</v>
       </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="O23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="n"/>
+      <c r="Z23" s="2" t="n"/>
+      <c r="AA23" s="2" t="n"/>
+      <c r="AB23" s="2" t="n"/>
+      <c r="AC23" s="2" t="n"/>
+      <c r="AD23" s="2" t="n"/>
+      <c r="AE23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>SE-ResNet-20</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="2" t="n">
         <v>0.295</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="2" t="n">
         <v>0.285</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="2" t="n">
         <v>0.245</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="J24" s="2" t="n">
         <v>0.355</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>0.355</v>
       </c>
+      <c r="O24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="X24" s="5" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>0.665</v>
+      </c>
     </row>
     <row r="25">
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="2" t="n">
         <v>0.19</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="2" t="n">
         <v>0.235</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" s="2" t="n">
         <v>0.165</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="J25" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>0.265</v>
       </c>
+      <c r="O25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AA25" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB25" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AC25" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AD25" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE25" s="2" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="26">
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="2" t="n">
         <v>0.17</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="2" t="n">
         <v>0.035</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="J26" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="27" s="9">
-      <c r="E27" s="3" t="n">
+      <c r="O26" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="2" t="n">
         <v>0.115</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" s="2" t="n">
         <v>0.125</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="J27" s="2" t="n">
         <v>0.175</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>0.165</v>
       </c>
-    </row>
-    <row r="28" s="9">
-      <c r="E28" s="3" t="n">
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="X27" s="2" t="n"/>
+      <c r="Y27" s="2" t="n"/>
+      <c r="Z27" s="2" t="n"/>
+      <c r="AA27" s="2" t="n"/>
+      <c r="AB27" s="2" t="n"/>
+      <c r="AC27" s="2" t="n"/>
+      <c r="AD27" s="2" t="n"/>
+      <c r="AE27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="2" t="n">
         <v>0.135</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="2" t="n">
         <v>0.025</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="J28" s="2" t="n">
         <v>0.175</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>0.18</v>
       </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="X28" s="2" t="n"/>
+      <c r="Y28" s="2" t="n"/>
+      <c r="Z28" s="2" t="n"/>
+      <c r="AA28" s="2" t="n"/>
+      <c r="AB28" s="2" t="n"/>
+      <c r="AC28" s="2" t="n"/>
+      <c r="AD28" s="2" t="n"/>
+      <c r="AE28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="2" t="n">
         <v>0.145</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.025</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="J29" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>0.21</v>
       </c>
+      <c r="O29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="X29" s="2" t="n"/>
+      <c r="Y29" s="2" t="n"/>
+      <c r="Z29" s="2" t="n"/>
+      <c r="AA29" s="2" t="n"/>
+      <c r="AB29" s="2" t="n"/>
+      <c r="AC29" s="2" t="n"/>
+      <c r="AD29" s="2" t="n"/>
+      <c r="AE29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" s="2" t="n">
         <v>0.14</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="J30" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>0.245</v>
       </c>
+      <c r="O30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X30" s="2" t="n"/>
+      <c r="Y30" s="2" t="n"/>
+      <c r="Z30" s="2" t="n"/>
+      <c r="AA30" s="2" t="n"/>
+      <c r="AB30" s="2" t="n"/>
+      <c r="AC30" s="2" t="n"/>
+      <c r="AD30" s="2" t="n"/>
+      <c r="AE30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="2" t="n">
         <v>0.195</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="2" t="n">
         <v>0.165</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="J31" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>0.29</v>
       </c>
+      <c r="O31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X31" s="2" t="n"/>
+      <c r="Y31" s="2" t="n"/>
+      <c r="Z31" s="2" t="n"/>
+      <c r="AA31" s="2" t="n"/>
+      <c r="AB31" s="2" t="n"/>
+      <c r="AC31" s="2" t="n"/>
+      <c r="AD31" s="2" t="n"/>
+      <c r="AE31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="2" t="n">
         <v>0.265</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="2" t="n">
         <v>0.005</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="J32" s="2" t="n">
         <v>0.425</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>0.345</v>
       </c>
-    </row>
-    <row r="33" s="9"/>
-    <row r="34" s="9">
-      <c r="D34" s="8" t="inlineStr">
+      <c r="O32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="X32" s="2" t="n"/>
+      <c r="Y32" s="2" t="n"/>
+      <c r="Z32" s="2" t="n"/>
+      <c r="AA32" s="2" t="n"/>
+      <c r="AB32" s="2" t="n"/>
+      <c r="AC32" s="2" t="n"/>
+      <c r="AD32" s="2" t="n"/>
+      <c r="AE32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n"/>
+      <c r="U33" s="2" t="n"/>
+      <c r="X33" s="2" t="n"/>
+      <c r="Y33" s="2" t="n"/>
+      <c r="Z33" s="2" t="n"/>
+      <c r="AA33" s="2" t="n"/>
+      <c r="AB33" s="2" t="n"/>
+      <c r="AC33" s="2" t="n"/>
+      <c r="AD33" s="2" t="n"/>
+      <c r="AE33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>DenseNet-BC-40</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="2" t="n">
         <v>0.385</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="2" t="n">
         <v>0.445</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="2" t="n">
         <v>0.435</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="2" t="n">
         <v>0.015</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="J34" s="2" t="n">
         <v>0.52</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>0.52</v>
       </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="X34" s="2" t="n"/>
+      <c r="Y34" s="2" t="n"/>
+      <c r="Z34" s="2" t="n"/>
+      <c r="AA34" s="2" t="n"/>
+      <c r="AB34" s="2" t="n"/>
+      <c r="AC34" s="2" t="n"/>
+      <c r="AD34" s="2" t="n"/>
+      <c r="AE34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="2" t="n">
         <v>0.285</v>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="J35" s="2" t="n">
         <v>0.425</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>0.42</v>
       </c>
+      <c r="O35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="X35" s="2" t="n"/>
+      <c r="Y35" s="2" t="n"/>
+      <c r="Z35" s="2" t="n"/>
+      <c r="AA35" s="2" t="n"/>
+      <c r="AB35" s="2" t="n"/>
+      <c r="AC35" s="2" t="n"/>
+      <c r="AD35" s="2" t="n"/>
+      <c r="AE35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" s="2" t="n">
         <v>0.045</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="J36" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>0.355</v>
       </c>
+      <c r="O36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="X36" s="2" t="n"/>
+      <c r="Y36" s="2" t="n"/>
+      <c r="Z36" s="2" t="n"/>
+      <c r="AA36" s="2" t="n"/>
+      <c r="AB36" s="2" t="n"/>
+      <c r="AC36" s="2" t="n"/>
+      <c r="AD36" s="2" t="n"/>
+      <c r="AE36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" s="2" t="n">
         <v>0.235</v>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" s="2" t="n">
         <v>0.075</v>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="J37" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>0.295</v>
       </c>
+      <c r="O37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X37" s="2" t="n"/>
+      <c r="Y37" s="2" t="n"/>
+      <c r="Z37" s="2" t="n"/>
+      <c r="AA37" s="2" t="n"/>
+      <c r="AB37" s="2" t="n"/>
+      <c r="AC37" s="2" t="n"/>
+      <c r="AD37" s="2" t="n"/>
+      <c r="AE37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="2" t="n">
         <v>0.195</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="2" t="n">
         <v>0.285</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="2" t="n">
         <v>0.06</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="J38" s="2" t="n">
         <v>0.265</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>0.335</v>
       </c>
-    </row>
-    <row r="39" s="9">
-      <c r="E39" s="3" t="n">
+      <c r="O38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X38" s="2" t="n"/>
+      <c r="Y38" s="2" t="n"/>
+      <c r="Z38" s="2" t="n"/>
+      <c r="AA38" s="2" t="n"/>
+      <c r="AB38" s="2" t="n"/>
+      <c r="AC38" s="2" t="n"/>
+      <c r="AD38" s="2" t="n"/>
+      <c r="AE38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="2" t="n">
         <v>0.355</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="J39" s="2" t="n">
         <v>0.32</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>0.335</v>
       </c>
-    </row>
-    <row r="40" s="9">
-      <c r="E40" s="3" t="n">
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
+      <c r="U39" s="2" t="n"/>
+      <c r="X39" s="2" t="n"/>
+      <c r="Y39" s="2" t="n"/>
+      <c r="Z39" s="2" t="n"/>
+      <c r="AA39" s="2" t="n"/>
+      <c r="AB39" s="2" t="n"/>
+      <c r="AC39" s="2" t="n"/>
+      <c r="AD39" s="2" t="n"/>
+      <c r="AE39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="2" t="n">
         <v>0.295</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="2" t="n">
         <v>0.32</v>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="J40" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>0.385</v>
       </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="n"/>
+      <c r="U40" s="2" t="n"/>
+      <c r="X40" s="2" t="n"/>
+      <c r="Y40" s="2" t="n"/>
+      <c r="Z40" s="2" t="n"/>
+      <c r="AA40" s="2" t="n"/>
+      <c r="AB40" s="2" t="n"/>
+      <c r="AC40" s="2" t="n"/>
+      <c r="AD40" s="2" t="n"/>
+      <c r="AE40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F41" s="2" t="n">
         <v>0.48</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="2" t="n">
         <v>0.535</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="2" t="n">
         <v>0.415</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="J41" s="2" t="n">
         <v>0.57</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>0.505</v>
       </c>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="n"/>
+      <c r="U41" s="2" t="n"/>
+      <c r="X41" s="2" t="n"/>
+      <c r="Y41" s="2" t="n"/>
+      <c r="Z41" s="2" t="n"/>
+      <c r="AA41" s="2" t="n"/>
+      <c r="AB41" s="2" t="n"/>
+      <c r="AC41" s="2" t="n"/>
+      <c r="AD41" s="2" t="n"/>
+      <c r="AE41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="2" t="n">
         <v>0.555</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="H42" s="2" t="n">
         <v>0.555</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" s="2" t="n">
         <v>0.025</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="J42" s="2" t="n">
         <v>0.615</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>0.625</v>
       </c>
-    </row>
-    <row r="43" ht="36" customHeight="1" s="9"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="n"/>
+      <c r="U42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
+      <c r="Z42" s="2" t="n"/>
+      <c r="AA42" s="2" t="n"/>
+      <c r="AB42" s="2" t="n"/>
+      <c r="AC42" s="2" t="n"/>
+      <c r="AD42" s="2" t="n"/>
+      <c r="AE42" s="2" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="6">
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="X43" s="2" t="n"/>
+      <c r="Y43" s="2" t="n"/>
+      <c r="Z43" s="2" t="n"/>
+      <c r="AA43" s="2" t="n"/>
+      <c r="AB43" s="2" t="n"/>
+      <c r="AC43" s="2" t="n"/>
+      <c r="AD43" s="2" t="n"/>
+      <c r="AE43" s="2" t="n"/>
+    </row>
     <row r="44">
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>RoR-3-110</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="2" t="n">
         <v>0.425</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="H44" s="2" t="n">
         <v>0.435</v>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="J44" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>0.51</v>
       </c>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
+      <c r="AA44" s="2" t="n"/>
+      <c r="AB44" s="2" t="n"/>
+      <c r="AC44" s="2" t="n"/>
+      <c r="AD44" s="2" t="n"/>
+      <c r="AE44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="2" t="n">
         <v>0.42</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="2" t="n">
         <v>0.415</v>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="J45" s="2" t="n">
         <v>0.025</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>0.46</v>
       </c>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="n"/>
+      <c r="U45" s="2" t="n"/>
+      <c r="X45" s="2" t="n"/>
+      <c r="Y45" s="2" t="n"/>
+      <c r="Z45" s="2" t="n"/>
+      <c r="AA45" s="2" t="n"/>
+      <c r="AB45" s="2" t="n"/>
+      <c r="AC45" s="2" t="n"/>
+      <c r="AD45" s="2" t="n"/>
+      <c r="AE45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="2" t="n">
         <v>0.335</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" s="2" t="n">
         <v>0.275</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="J46" s="2" t="n">
         <v>0.065</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>0.37</v>
       </c>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
+      <c r="Q46" s="2" t="n"/>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
+      <c r="U46" s="2" t="n"/>
+      <c r="X46" s="2" t="n"/>
+      <c r="Y46" s="2" t="n"/>
+      <c r="Z46" s="2" t="n"/>
+      <c r="AA46" s="2" t="n"/>
+      <c r="AB46" s="2" t="n"/>
+      <c r="AC46" s="2" t="n"/>
+      <c r="AD46" s="2" t="n"/>
+      <c r="AE46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="2" t="n">
         <v>0.305</v>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="2" t="n">
         <v>0.35</v>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="2" t="n">
         <v>0.315</v>
       </c>
-      <c r="I47" s="3" t="n">
+      <c r="I47" s="2" t="n">
         <v>0.28</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="J47" s="2" t="n">
         <v>0.12</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>0.325</v>
       </c>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
+      <c r="Q47" s="2" t="n"/>
+      <c r="R47" s="2" t="n"/>
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="2" t="n"/>
+      <c r="U47" s="2" t="n"/>
+      <c r="X47" s="2" t="n"/>
+      <c r="Y47" s="2" t="n"/>
+      <c r="Z47" s="2" t="n"/>
+      <c r="AA47" s="2" t="n"/>
+      <c r="AB47" s="2" t="n"/>
+      <c r="AC47" s="2" t="n"/>
+      <c r="AD47" s="2" t="n"/>
+      <c r="AE47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="F48" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="2" t="n">
         <v>0.325</v>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="H48" s="2" t="n">
         <v>0.305</v>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I48" s="2" t="n">
         <v>0.245</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="J48" s="2" t="n">
         <v>0.125</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>0.31</v>
       </c>
-    </row>
-    <row r="49" s="9">
-      <c r="E49" s="3" t="n">
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n"/>
+      <c r="Q48" s="2" t="n"/>
+      <c r="R48" s="2" t="n"/>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="n"/>
+      <c r="U48" s="2" t="n"/>
+      <c r="X48" s="2" t="n"/>
+      <c r="Y48" s="2" t="n"/>
+      <c r="Z48" s="2" t="n"/>
+      <c r="AA48" s="2" t="n"/>
+      <c r="AB48" s="2" t="n"/>
+      <c r="AC48" s="2" t="n"/>
+      <c r="AD48" s="2" t="n"/>
+      <c r="AE48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="2" t="n">
         <v>0.225</v>
       </c>
-      <c r="G49" s="3" t="n">
+      <c r="G49" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" s="2" t="n">
         <v>0.265</v>
       </c>
-      <c r="I49" s="3" t="n">
+      <c r="I49" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="J49" s="3" t="n">
+      <c r="J49" s="2" t="n">
         <v>0.095</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>0.275</v>
       </c>
-    </row>
-    <row r="50" s="9">
-      <c r="E50" s="3" t="n">
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="2" t="n"/>
+      <c r="S49" s="2" t="n"/>
+      <c r="T49" s="2" t="n"/>
+      <c r="U49" s="2" t="n"/>
+      <c r="X49" s="2" t="n"/>
+      <c r="Y49" s="2" t="n"/>
+      <c r="Z49" s="2" t="n"/>
+      <c r="AA49" s="2" t="n"/>
+      <c r="AB49" s="2" t="n"/>
+      <c r="AC49" s="2" t="n"/>
+      <c r="AD49" s="2" t="n"/>
+      <c r="AE49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="H50" s="3" t="n">
+      <c r="H50" s="2" t="n">
         <v>0.24</v>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="J50" s="2" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" s="2" t="n">
         <v>0.265</v>
       </c>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
+      <c r="Q50" s="2" t="n"/>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="2" t="n"/>
+      <c r="T50" s="2" t="n"/>
+      <c r="U50" s="2" t="n"/>
+      <c r="X50" s="2" t="n"/>
+      <c r="Y50" s="2" t="n"/>
+      <c r="Z50" s="2" t="n"/>
+      <c r="AA50" s="2" t="n"/>
+      <c r="AB50" s="2" t="n"/>
+      <c r="AC50" s="2" t="n"/>
+      <c r="AD50" s="2" t="n"/>
+      <c r="AE50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="2" t="n">
         <v>0.24</v>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="I51" s="2" t="n">
         <v>0.205</v>
       </c>
-      <c r="J51" s="3" t="n">
+      <c r="J51" s="2" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" s="2" t="n">
         <v>0.305</v>
       </c>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
+      <c r="Q51" s="2" t="n"/>
+      <c r="R51" s="2" t="n"/>
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="2" t="n"/>
+      <c r="U51" s="2" t="n"/>
+      <c r="X51" s="2" t="n"/>
+      <c r="Y51" s="2" t="n"/>
+      <c r="Z51" s="2" t="n"/>
+      <c r="AA51" s="2" t="n"/>
+      <c r="AB51" s="2" t="n"/>
+      <c r="AC51" s="2" t="n"/>
+      <c r="AD51" s="2" t="n"/>
+      <c r="AE51" s="2" t="n"/>
     </row>
     <row r="52">
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="F52" s="2" t="n">
         <v>0.24</v>
       </c>
-      <c r="G52" s="3" t="n">
+      <c r="G52" s="2" t="n">
         <v>0.325</v>
       </c>
-      <c r="H52" s="3" t="n">
+      <c r="H52" s="2" t="n">
         <v>0.235</v>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="I52" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="J52" s="3" t="n">
+      <c r="J52" s="2" t="n">
         <v>0.065</v>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" s="2" t="n">
         <v>0.33</v>
       </c>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
+      <c r="Q52" s="2" t="n"/>
+      <c r="R52" s="2" t="n"/>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="n"/>
+      <c r="U52" s="2" t="n"/>
+      <c r="X52" s="2" t="n"/>
+      <c r="Y52" s="2" t="n"/>
+      <c r="Z52" s="2" t="n"/>
+      <c r="AA52" s="2" t="n"/>
+      <c r="AB52" s="2" t="n"/>
+      <c r="AC52" s="2" t="n"/>
+      <c r="AD52" s="2" t="n"/>
+      <c r="AE52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
+      <c r="Q53" s="2" t="n"/>
+      <c r="R53" s="2" t="n"/>
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="2" t="n"/>
+      <c r="U53" s="2" t="n"/>
+      <c r="X53" s="2" t="n"/>
+      <c r="Y53" s="2" t="n"/>
+      <c r="Z53" s="2" t="n"/>
+      <c r="AA53" s="2" t="n"/>
+      <c r="AB53" s="2" t="n"/>
+      <c r="AC53" s="2" t="n"/>
+      <c r="AD53" s="2" t="n"/>
+      <c r="AE53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>DIA-PreResNet-56</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="F54" s="2" t="n">
         <v>0.445</v>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="2" t="n">
         <v>0.435</v>
       </c>
-      <c r="H54" s="3" t="n">
+      <c r="H54" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="I54" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="J54" s="2" t="n">
         <v>0.495</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" s="2" t="n">
         <v>0.195</v>
       </c>
-    </row>
-    <row r="55" s="9">
-      <c r="E55" s="3" t="n">
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="n"/>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="n"/>
+      <c r="U54" s="2" t="n"/>
+      <c r="X54" s="2" t="n"/>
+      <c r="Y54" s="2" t="n"/>
+      <c r="Z54" s="2" t="n"/>
+      <c r="AA54" s="2" t="n"/>
+      <c r="AB54" s="2" t="n"/>
+      <c r="AC54" s="2" t="n"/>
+      <c r="AD54" s="2" t="n"/>
+      <c r="AE54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="2" t="n">
         <v>0.435</v>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="H55" s="3" t="n">
+      <c r="H55" s="2" t="n">
         <v>0.445</v>
       </c>
-      <c r="I55" s="3" t="n">
+      <c r="I55" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="J55" s="3" t="n">
+      <c r="J55" s="2" t="n">
         <v>0.465</v>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" s="2" t="n">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="56" s="9">
-      <c r="E56" s="3" t="n">
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="2" t="n"/>
+      <c r="U55" s="2" t="n"/>
+      <c r="X55" s="2" t="n"/>
+      <c r="Y55" s="2" t="n"/>
+      <c r="Z55" s="2" t="n"/>
+      <c r="AA55" s="2" t="n"/>
+      <c r="AB55" s="2" t="n"/>
+      <c r="AC55" s="2" t="n"/>
+      <c r="AD55" s="2" t="n"/>
+      <c r="AE55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="H56" s="3" t="n">
+      <c r="H56" s="2" t="n">
         <v>0.445</v>
       </c>
-      <c r="I56" s="3" t="n">
+      <c r="I56" s="2" t="n">
         <v>0.445</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="J56" s="2" t="n">
         <v>0.47</v>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="K56" s="2" t="n">
         <v>0.265</v>
       </c>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
+      <c r="R56" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="n"/>
+      <c r="U56" s="2" t="n"/>
+      <c r="X56" s="2" t="n"/>
+      <c r="Y56" s="2" t="n"/>
+      <c r="Z56" s="2" t="n"/>
+      <c r="AA56" s="2" t="n"/>
+      <c r="AB56" s="2" t="n"/>
+      <c r="AC56" s="2" t="n"/>
+      <c r="AD56" s="2" t="n"/>
+      <c r="AE56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="2" t="n">
         <v>0.37</v>
       </c>
-      <c r="H57" s="3" t="n">
+      <c r="H57" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="I57" s="3" t="n">
+      <c r="I57" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="J57" s="3" t="n">
+      <c r="J57" s="2" t="n">
         <v>0.385</v>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" s="2" t="n">
         <v>0.225</v>
       </c>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+      <c r="R57" s="2" t="n"/>
+      <c r="S57" s="2" t="n"/>
+      <c r="T57" s="2" t="n"/>
+      <c r="U57" s="2" t="n"/>
+      <c r="X57" s="2" t="n"/>
+      <c r="Y57" s="2" t="n"/>
+      <c r="Z57" s="2" t="n"/>
+      <c r="AA57" s="2" t="n"/>
+      <c r="AB57" s="2" t="n"/>
+      <c r="AC57" s="2" t="n"/>
+      <c r="AD57" s="2" t="n"/>
+      <c r="AE57" s="2" t="n"/>
     </row>
     <row r="58">
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="2" t="n">
         <v>0.295</v>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="H58" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="I58" s="2" t="n">
         <v>0.295</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="J58" s="2" t="n">
         <v>0.32</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" s="2" t="n">
         <v>0.195</v>
       </c>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
+      <c r="Q58" s="2" t="n"/>
+      <c r="R58" s="2" t="n"/>
+      <c r="S58" s="2" t="n"/>
+      <c r="T58" s="2" t="n"/>
+      <c r="U58" s="2" t="n"/>
+      <c r="X58" s="2" t="n"/>
+      <c r="Y58" s="2" t="n"/>
+      <c r="Z58" s="2" t="n"/>
+      <c r="AA58" s="2" t="n"/>
+      <c r="AB58" s="2" t="n"/>
+      <c r="AC58" s="2" t="n"/>
+      <c r="AD58" s="2" t="n"/>
+      <c r="AE58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F59" s="2" t="n">
         <v>0.24</v>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G59" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="H59" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="I59" s="3" t="n">
+      <c r="I59" s="2" t="n">
         <v>0.265</v>
       </c>
-      <c r="J59" s="3" t="n">
+      <c r="J59" s="2" t="n">
         <v>0.27</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" s="2" t="n">
         <v>0.175</v>
       </c>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
+      <c r="P59" s="2" t="n"/>
+      <c r="Q59" s="2" t="n"/>
+      <c r="R59" s="2" t="n"/>
+      <c r="S59" s="2" t="n"/>
+      <c r="T59" s="2" t="n"/>
+      <c r="U59" s="2" t="n"/>
+      <c r="X59" s="2" t="n"/>
+      <c r="Y59" s="2" t="n"/>
+      <c r="Z59" s="2" t="n"/>
+      <c r="AA59" s="2" t="n"/>
+      <c r="AB59" s="2" t="n"/>
+      <c r="AC59" s="2" t="n"/>
+      <c r="AD59" s="2" t="n"/>
+      <c r="AE59" s="2" t="n"/>
     </row>
     <row r="60">
-      <c r="E60" s="3" t="n">
+      <c r="E60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F60" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" s="2" t="n">
         <v>0.265</v>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="H60" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I60" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="J60" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" s="2" t="n">
         <v>0.125</v>
       </c>
-    </row>
-    <row r="61" s="9">
-      <c r="E61" s="3" t="n">
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
+      <c r="Q60" s="2" t="n"/>
+      <c r="R60" s="2" t="n"/>
+      <c r="S60" s="2" t="n"/>
+      <c r="T60" s="2" t="n"/>
+      <c r="U60" s="2" t="n"/>
+      <c r="X60" s="2" t="n"/>
+      <c r="Y60" s="2" t="n"/>
+      <c r="Z60" s="2" t="n"/>
+      <c r="AA60" s="2" t="n"/>
+      <c r="AB60" s="2" t="n"/>
+      <c r="AC60" s="2" t="n"/>
+      <c r="AD60" s="2" t="n"/>
+      <c r="AE60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F61" s="3" t="n">
+      <c r="F61" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="G61" s="3" t="n">
+      <c r="G61" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="H61" s="3" t="n">
+      <c r="H61" s="2" t="n">
         <v>0.205</v>
       </c>
-      <c r="I61" s="3" t="n">
+      <c r="I61" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="J61" s="3" t="n">
+      <c r="J61" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" s="2" t="n">
         <v>0.08500000000000001</v>
       </c>
-    </row>
-    <row r="62" s="9">
-      <c r="E62" s="3" t="n">
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="n"/>
+      <c r="Q61" s="2" t="n"/>
+      <c r="R61" s="2" t="n"/>
+      <c r="S61" s="2" t="n"/>
+      <c r="T61" s="2" t="n"/>
+      <c r="U61" s="2" t="n"/>
+      <c r="X61" s="2" t="n"/>
+      <c r="Y61" s="2" t="n"/>
+      <c r="Z61" s="2" t="n"/>
+      <c r="AA61" s="2" t="n"/>
+      <c r="AB61" s="2" t="n"/>
+      <c r="AC61" s="2" t="n"/>
+      <c r="AD61" s="2" t="n"/>
+      <c r="AE61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="F62" s="2" t="n">
         <v>0.26</v>
       </c>
-      <c r="G62" s="3" t="n">
+      <c r="G62" s="2" t="n">
         <v>0.32</v>
       </c>
-      <c r="H62" s="3" t="n">
+      <c r="H62" s="2" t="n">
         <v>0.215</v>
       </c>
-      <c r="I62" s="3" t="n">
+      <c r="I62" s="2" t="n">
         <v>0.275</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="J62" s="2" t="n">
         <v>0.34</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="K62" s="2" t="n">
         <v>0.075</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="F65" s="11" t="inlineStr">
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
+      <c r="P62" s="2" t="n"/>
+      <c r="Q62" s="2" t="n"/>
+      <c r="R62" s="2" t="n"/>
+      <c r="S62" s="2" t="n"/>
+      <c r="T62" s="2" t="n"/>
+      <c r="U62" s="2" t="n"/>
+      <c r="X62" s="2" t="n"/>
+      <c r="Y62" s="2" t="n"/>
+      <c r="Z62" s="2" t="n"/>
+      <c r="AA62" s="2" t="n"/>
+      <c r="AB62" s="2" t="n"/>
+      <c r="AC62" s="2" t="n"/>
+      <c r="AD62" s="2" t="n"/>
+      <c r="AE62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
+      <c r="Q63" s="2" t="n"/>
+      <c r="R63" s="2" t="n"/>
+      <c r="S63" s="2" t="n"/>
+      <c r="T63" s="2" t="n"/>
+      <c r="U63" s="2" t="n"/>
+      <c r="X63" s="2" t="n"/>
+      <c r="Y63" s="2" t="n"/>
+      <c r="Z63" s="2" t="n"/>
+      <c r="AA63" s="2" t="n"/>
+      <c r="AB63" s="2" t="n"/>
+      <c r="AC63" s="2" t="n"/>
+      <c r="AD63" s="2" t="n"/>
+      <c r="AE63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
+      <c r="Q64" s="2" t="n"/>
+      <c r="R64" s="2" t="n"/>
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="2" t="n"/>
+      <c r="U64" s="2" t="n"/>
+      <c r="X64" s="2" t="n"/>
+      <c r="Y64" s="2" t="n"/>
+      <c r="Z64" s="2" t="n"/>
+      <c r="AA64" s="2" t="n"/>
+      <c r="AB64" s="2" t="n"/>
+      <c r="AC64" s="2" t="n"/>
+      <c r="AD64" s="2" t="n"/>
+      <c r="AE64" s="2" t="n"/>
+    </row>
+    <row r="65" ht="72" customHeight="1" s="6">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>黑盒攻击损失值（越大攻击效果越好）(N=5)</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="D66" s="2" t="inlineStr">
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>邻域样本数影响损失值（越大攻击效果越好）(beta=2.5)</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="n"/>
+      <c r="R65" s="2" t="n"/>
+      <c r="S65" s="2" t="n"/>
+      <c r="T65" s="2" t="n"/>
+      <c r="U65" s="2" t="n"/>
+      <c r="X65" s="2" t="n"/>
+      <c r="Y65" s="2" t="n"/>
+      <c r="Z65" s="4" t="inlineStr">
+        <is>
+          <t>不同攻击方法影响损失值（越大攻击效果越好）</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="n"/>
+      <c r="AB65" s="2" t="n"/>
+      <c r="AC65" s="2" t="n"/>
+      <c r="AD65" s="2" t="n"/>
+      <c r="AE65" s="2" t="n"/>
+    </row>
+    <row r="66" ht="36" customHeight="1" s="6">
+      <c r="D66" s="1" t="inlineStr">
         <is>
           <t>代理模型</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="1" t="inlineStr">
         <is>
           <t>ResNet-5</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>SE-PreResNet-110</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="1" t="inlineStr">
         <is>
           <t>SE-ResNet-20</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="I66" s="1" t="inlineStr">
         <is>
           <t>DenseNet-BC-40（k=12）</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="1" t="inlineStr">
         <is>
           <t>RoR-3-110</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="1" t="inlineStr">
         <is>
           <t>DIA-PreResNet-56</t>
         </is>
       </c>
-    </row>
-    <row r="67" s="9">
-      <c r="D67" s="8" t="inlineStr">
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t>代理模型</t>
+        </is>
+      </c>
+      <c r="O66" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P66" s="1" t="inlineStr">
+        <is>
+          <t>ResNet-5</t>
+        </is>
+      </c>
+      <c r="Q66" s="1" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="R66" s="1" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="S66" s="1" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40（k=12）</t>
+        </is>
+      </c>
+      <c r="T66" s="1" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="U66" s="1" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+      <c r="X66" s="1" t="inlineStr">
+        <is>
+          <t>代理模型</t>
+        </is>
+      </c>
+      <c r="Y66" s="1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="Z66" s="1" t="inlineStr">
+        <is>
+          <t>ResNet-5</t>
+        </is>
+      </c>
+      <c r="AA66" s="1" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="AB66" s="1" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40（k=12）</t>
+        </is>
+      </c>
+      <c r="AC66" s="1" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40?k=12?</t>
+        </is>
+      </c>
+      <c r="AD66" s="1" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="AE66" s="1" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>ResNet-56</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="F67" s="2" t="n">
         <v>9.960459999999999</v>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="G67" s="2" t="n">
         <v>2.63602</v>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="H67" s="2" t="n">
         <v>2.93902</v>
       </c>
-      <c r="I67" s="3" t="n">
+      <c r="I67" s="2" t="n">
         <v>3.5534</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="J67" s="2" t="n">
         <v>2.4141</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K67" s="2" t="n">
         <v>3.18371</v>
       </c>
-    </row>
-    <row r="68" s="9">
-      <c r="E68" s="3" t="n">
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>ResNet-56</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>9.960459999999999</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>2.63602</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>2.93902</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>3.5534</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>2.4141</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>3.18371</v>
+      </c>
+      <c r="X67" s="5" t="inlineStr">
+        <is>
+          <t>ResNet-56</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="n">
+        <v>2.51945</v>
+      </c>
+      <c r="AA67" s="2" t="n">
+        <v>1.18806</v>
+      </c>
+      <c r="AB67" s="2" t="n">
+        <v>1.40728</v>
+      </c>
+      <c r="AC67" s="2" t="n">
+        <v>1.86862</v>
+      </c>
+      <c r="AD67" s="2" t="n">
+        <v>1.23278</v>
+      </c>
+      <c r="AE67" s="2" t="n">
+        <v>1.67401</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="F68" s="2" t="n">
         <v>9.156409999999999</v>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="G68" s="2" t="n">
         <v>2.89706</v>
       </c>
-      <c r="H68" s="3" t="n">
+      <c r="H68" s="2" t="n">
         <v>3.42002</v>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="I68" s="2" t="n">
         <v>4.01273</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="J68" s="2" t="n">
         <v>2.78511</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" s="2" t="n">
         <v>3.53974</v>
       </c>
+      <c r="O68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>7.59767</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>2.8952</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>4.40358</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>4.35279</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>2.83398</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>4.4333</v>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="n">
+        <v>11.74236</v>
+      </c>
+      <c r="AA68" s="2" t="n">
+        <v>1.83726</v>
+      </c>
+      <c r="AB68" s="2" t="n">
+        <v>1.82497</v>
+      </c>
+      <c r="AC68" s="2" t="n">
+        <v>2.3986</v>
+      </c>
+      <c r="AD68" s="2" t="n">
+        <v>1.58301</v>
+      </c>
+      <c r="AE68" s="2" t="n">
+        <v>1.78431</v>
+      </c>
     </row>
     <row r="69">
-      <c r="E69" s="3" t="n">
+      <c r="E69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="F69" s="2" t="n">
         <v>7.97424</v>
       </c>
-      <c r="G69" s="3" t="n">
+      <c r="G69" s="2" t="n">
         <v>2.97441</v>
       </c>
-      <c r="H69" s="3" t="n">
+      <c r="H69" s="2" t="n">
         <v>3.91685</v>
       </c>
-      <c r="I69" s="3" t="n">
+      <c r="I69" s="2" t="n">
         <v>4.13877</v>
       </c>
-      <c r="J69" s="3" t="n">
+      <c r="J69" s="2" t="n">
         <v>2.87134</v>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" s="2" t="n">
         <v>3.97842</v>
       </c>
+      <c r="O69" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>7.96792</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>3.13278</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>4.83417</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>4.80394</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>3.10876</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>4.7845</v>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="n">
+        <v>9.960459999999999</v>
+      </c>
+      <c r="AA69" s="2" t="n">
+        <v>2.63602</v>
+      </c>
+      <c r="AB69" s="2" t="n">
+        <v>2.93902</v>
+      </c>
+      <c r="AC69" s="2" t="n">
+        <v>3.5534</v>
+      </c>
+      <c r="AD69" s="2" t="n">
+        <v>2.4141</v>
+      </c>
+      <c r="AE69" s="2" t="n">
+        <v>3.18371</v>
+      </c>
     </row>
     <row r="70">
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="2" t="n">
         <v>7.44392</v>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="G70" s="2" t="n">
         <v>2.98016</v>
       </c>
-      <c r="H70" s="3" t="n">
+      <c r="H70" s="2" t="n">
         <v>4.24909</v>
       </c>
-      <c r="I70" s="3" t="n">
+      <c r="I70" s="2" t="n">
         <v>4.25111</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="J70" s="2" t="n">
         <v>2.92426</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" s="2" t="n">
         <v>4.36281</v>
       </c>
+      <c r="O70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>8.11393</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>3.25768</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>5.08779</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>5.01659</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>3.24309</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>5.05063</v>
+      </c>
+      <c r="X70" s="2" t="n"/>
+      <c r="Y70" s="2" t="n"/>
+      <c r="Z70" s="2" t="n"/>
+      <c r="AA70" s="2" t="n"/>
+      <c r="AB70" s="2" t="n"/>
+      <c r="AC70" s="2" t="n"/>
+      <c r="AD70" s="2" t="n"/>
+      <c r="AE70" s="2" t="n"/>
     </row>
     <row r="71">
-      <c r="E71" s="3" t="n">
+      <c r="E71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F71" s="3" t="n">
+      <c r="F71" s="2" t="n">
         <v>7.17928</v>
       </c>
-      <c r="G71" s="3" t="n">
+      <c r="G71" s="2" t="n">
         <v>2.95681</v>
       </c>
-      <c r="H71" s="3" t="n">
+      <c r="H71" s="2" t="n">
         <v>4.43675</v>
       </c>
-      <c r="I71" s="3" t="n">
+      <c r="I71" s="2" t="n">
         <v>4.33715</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="J71" s="2" t="n">
         <v>2.90341</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="2" t="n">
         <v>4.56025</v>
       </c>
+      <c r="O71" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>8.03805</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>3.28706</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>4.94984</v>
+      </c>
+      <c r="S71" s="2" t="n">
+        <v>5.01856</v>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>3.2545</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>5.03854</v>
+      </c>
+      <c r="X71" s="5" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="n">
+        <v>2.16811</v>
+      </c>
+      <c r="AA71" s="2" t="n">
+        <v>1.54482</v>
+      </c>
+      <c r="AB71" s="2" t="n">
+        <v>1.54023</v>
+      </c>
+      <c r="AC71" s="2" t="n">
+        <v>1.98681</v>
+      </c>
+      <c r="AD71" s="2" t="n">
+        <v>1.27502</v>
+      </c>
+      <c r="AE71" s="2" t="n">
+        <v>1.56654</v>
+      </c>
     </row>
     <row r="72">
-      <c r="E72" s="3" t="n">
+      <c r="E72" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="F72" s="2" t="n">
         <v>7.59767</v>
       </c>
-      <c r="G72" s="3" t="n">
+      <c r="G72" s="2" t="n">
         <v>2.8952</v>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="H72" s="2" t="n">
         <v>4.40358</v>
       </c>
-      <c r="I72" s="3" t="n">
+      <c r="I72" s="2" t="n">
         <v>4.35279</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="J72" s="2" t="n">
         <v>2.83398</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" s="2" t="n">
         <v>4.4333</v>
       </c>
-    </row>
-    <row r="73" s="9">
-      <c r="E73" s="3" t="n">
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="n"/>
+      <c r="Q72" s="2" t="n"/>
+      <c r="R72" s="2" t="n"/>
+      <c r="S72" s="2" t="n"/>
+      <c r="T72" s="2" t="n"/>
+      <c r="U72" s="2" t="n"/>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="n">
+        <v>3.08854</v>
+      </c>
+      <c r="AA72" s="2" t="n">
+        <v>12.49768</v>
+      </c>
+      <c r="AB72" s="2" t="n">
+        <v>2.25772</v>
+      </c>
+      <c r="AC72" s="2" t="n">
+        <v>2.88281</v>
+      </c>
+      <c r="AD72" s="2" t="n">
+        <v>1.94957</v>
+      </c>
+      <c r="AE72" s="2" t="n">
+        <v>2.18859</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="E73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="2" t="n">
         <v>7.80579</v>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="2" t="n">
         <v>2.69823</v>
       </c>
-      <c r="H73" s="3" t="n">
+      <c r="H73" s="2" t="n">
         <v>4.08547</v>
       </c>
-      <c r="I73" s="3" t="n">
+      <c r="I73" s="2" t="n">
         <v>4.17524</v>
       </c>
-      <c r="J73" s="3" t="n">
+      <c r="J73" s="2" t="n">
         <v>2.65719</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="2" t="n">
         <v>4.14313</v>
       </c>
-    </row>
-    <row r="74" s="9">
-      <c r="E74" s="3" t="n">
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>SE-PreResNet-110</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>4.38148</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>9.95201</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>3.37386</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>3.81884</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>2.80962</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>3.47645</v>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="n">
+        <v>4.38148</v>
+      </c>
+      <c r="AA73" s="2" t="n">
+        <v>9.95201</v>
+      </c>
+      <c r="AB73" s="2" t="n">
+        <v>3.37386</v>
+      </c>
+      <c r="AC73" s="2" t="n">
+        <v>3.81884</v>
+      </c>
+      <c r="AD73" s="2" t="n">
+        <v>2.80962</v>
+      </c>
+      <c r="AE73" s="2" t="n">
+        <v>3.47645</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="E74" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F74" s="2" t="n">
         <v>7.88552</v>
       </c>
-      <c r="G74" s="3" t="n">
+      <c r="G74" s="2" t="n">
         <v>2.35188</v>
       </c>
-      <c r="H74" s="3" t="n">
+      <c r="H74" s="2" t="n">
         <v>3.40819</v>
       </c>
-      <c r="I74" s="3" t="n">
+      <c r="I74" s="2" t="n">
         <v>3.81749</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="J74" s="2" t="n">
         <v>2.39622</v>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="K74" s="2" t="n">
         <v>3.52071</v>
       </c>
+      <c r="O74" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>5.83259</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>5.67627</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>4.46957</v>
+      </c>
+      <c r="S74" s="2" t="n">
+        <v>4.67463</v>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>3.3086</v>
+      </c>
+      <c r="U74" s="2" t="n">
+        <v>4.82279</v>
+      </c>
+      <c r="X74" s="2" t="n"/>
+      <c r="Y74" s="2" t="n"/>
+      <c r="Z74" s="2" t="n"/>
+      <c r="AA74" s="2" t="n"/>
+      <c r="AB74" s="2" t="n"/>
+      <c r="AC74" s="2" t="n"/>
+      <c r="AD74" s="2" t="n"/>
+      <c r="AE74" s="2" t="n"/>
     </row>
     <row r="75">
-      <c r="E75" s="3" t="n">
+      <c r="E75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="2" t="n">
         <v>7.83443</v>
       </c>
-      <c r="G75" s="3" t="n">
+      <c r="G75" s="2" t="n">
         <v>1.99529</v>
       </c>
-      <c r="H75" s="3" t="n">
+      <c r="H75" s="2" t="n">
         <v>2.83184</v>
       </c>
-      <c r="I75" s="3" t="n">
+      <c r="I75" s="2" t="n">
         <v>3.23933</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="J75" s="2" t="n">
         <v>1.8864</v>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="K75" s="2" t="n">
         <v>2.79115</v>
       </c>
+      <c r="O75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>5.95836</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>6.1051</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>4.90455</v>
+      </c>
+      <c r="S75" s="2" t="n">
+        <v>4.88601</v>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>3.62051</v>
+      </c>
+      <c r="U75" s="2" t="n">
+        <v>5.19733</v>
+      </c>
+      <c r="X75" s="5" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="n">
+        <v>2.3636</v>
+      </c>
+      <c r="AA75" s="2" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AB75" s="2" t="n">
+        <v>2.87349</v>
+      </c>
+      <c r="AC75" s="2" t="n">
+        <v>1.95013</v>
+      </c>
+      <c r="AD75" s="2" t="n">
+        <v>1.37599</v>
+      </c>
+      <c r="AE75" s="2" t="n">
+        <v>1.90736</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="O76" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>6.1805</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>6.36747</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>4.94838</v>
+      </c>
+      <c r="S76" s="2" t="n">
+        <v>5.21524</v>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>3.72192</v>
+      </c>
+      <c r="U76" s="2" t="n">
+        <v>5.4032</v>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="n">
+        <v>2.57292</v>
+      </c>
+      <c r="AA76" s="2" t="n">
+        <v>1.72953</v>
+      </c>
+      <c r="AB76" s="2" t="n">
+        <v>13.11883</v>
+      </c>
+      <c r="AC76" s="2" t="n">
+        <v>2.37495</v>
+      </c>
+      <c r="AD76" s="2" t="n">
+        <v>1.38532</v>
+      </c>
+      <c r="AE76" s="2" t="n">
+        <v>1.79829</v>
+      </c>
     </row>
     <row r="77">
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>SE-PreResNet-110</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="2" t="n">
         <v>4.38148</v>
       </c>
-      <c r="G77" s="3" t="n">
+      <c r="G77" s="2" t="n">
         <v>9.95201</v>
       </c>
-      <c r="H77" s="3" t="n">
+      <c r="H77" s="2" t="n">
         <v>3.37386</v>
       </c>
-      <c r="I77" s="3" t="n">
+      <c r="I77" s="2" t="n">
         <v>3.81884</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="J77" s="2" t="n">
         <v>2.80962</v>
       </c>
-      <c r="K77" s="3" t="n">
+      <c r="K77" s="2" t="n">
         <v>3.47645</v>
       </c>
-    </row>
-    <row r="78" s="9">
-      <c r="E78" s="3" t="n">
+      <c r="O77" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>6.1937</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>6.45249</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>4.96015</v>
+      </c>
+      <c r="S77" s="2" t="n">
+        <v>5.25108</v>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>3.82094</v>
+      </c>
+      <c r="U77" s="2" t="n">
+        <v>5.52543</v>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="n">
+        <v>4.43778</v>
+      </c>
+      <c r="AA77" s="2" t="n">
+        <v>2.68155</v>
+      </c>
+      <c r="AB77" s="2" t="n">
+        <v>12.39732</v>
+      </c>
+      <c r="AC77" s="2" t="n">
+        <v>3.80847</v>
+      </c>
+      <c r="AD77" s="2" t="n">
+        <v>2.39275</v>
+      </c>
+      <c r="AE77" s="2" t="n">
+        <v>3.38826</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="E78" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="2" t="n">
         <v>4.81055</v>
       </c>
-      <c r="G78" s="3" t="n">
+      <c r="G78" s="2" t="n">
         <v>8.91596</v>
       </c>
-      <c r="H78" s="3" t="n">
+      <c r="H78" s="2" t="n">
         <v>3.73428</v>
       </c>
-      <c r="I78" s="3" t="n">
+      <c r="I78" s="2" t="n">
         <v>4.23355</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="J78" s="2" t="n">
         <v>3.18687</v>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="K78" s="2" t="n">
         <v>4.2622</v>
       </c>
-    </row>
-    <row r="79" s="9">
-      <c r="E79" s="3" t="n">
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="n"/>
+      <c r="Q78" s="2" t="n"/>
+      <c r="R78" s="2" t="n"/>
+      <c r="S78" s="2" t="n"/>
+      <c r="T78" s="2" t="n"/>
+      <c r="U78" s="2" t="n"/>
+      <c r="X78" s="2" t="n"/>
+      <c r="Y78" s="2" t="n"/>
+      <c r="Z78" s="2" t="n"/>
+      <c r="AA78" s="2" t="n"/>
+      <c r="AB78" s="2" t="n"/>
+      <c r="AC78" s="2" t="n"/>
+      <c r="AD78" s="2" t="n"/>
+      <c r="AE78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="2" t="n">
         <v>5.09863</v>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="2" t="n">
         <v>7.66787</v>
       </c>
-      <c r="H79" s="3" t="n">
+      <c r="H79" s="2" t="n">
         <v>4.25727</v>
       </c>
-      <c r="I79" s="3" t="n">
+      <c r="I79" s="2" t="n">
         <v>4.46174</v>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="J79" s="2" t="n">
         <v>3.46495</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="K79" s="2" t="n">
         <v>4.70913</v>
       </c>
-    </row>
-    <row r="80" s="9">
-      <c r="E80" s="3" t="n">
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>SE-ResNet-20</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>4.43778</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>2.68155</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>12.39732</v>
+      </c>
+      <c r="S79" s="2" t="n">
+        <v>3.80847</v>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>2.39275</v>
+      </c>
+      <c r="U79" s="2" t="n">
+        <v>3.38826</v>
+      </c>
+      <c r="X79" s="5" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="n">
+        <v>1.87253</v>
+      </c>
+      <c r="AA79" s="2" t="n">
+        <v>1.11741</v>
+      </c>
+      <c r="AB79" s="2" t="n">
+        <v>1.28818</v>
+      </c>
+      <c r="AC79" s="2" t="n">
+        <v>2.3303</v>
+      </c>
+      <c r="AD79" s="2" t="n">
+        <v>1.05959</v>
+      </c>
+      <c r="AE79" s="2" t="n">
+        <v>1.30224</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="E80" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="2" t="n">
         <v>5.50833</v>
       </c>
-      <c r="G80" s="3" t="n">
+      <c r="G80" s="2" t="n">
         <v>6.76992</v>
       </c>
-      <c r="H80" s="3" t="n">
+      <c r="H80" s="2" t="n">
         <v>4.44884</v>
       </c>
-      <c r="I80" s="3" t="n">
+      <c r="I80" s="2" t="n">
         <v>4.65787</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="J80" s="2" t="n">
         <v>3.49636</v>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="K80" s="2" t="n">
         <v>4.92523</v>
       </c>
+      <c r="O80" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>5.96045</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>3.22363</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>8.05494</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>4.9347</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>2.83232</v>
+      </c>
+      <c r="U80" s="2" t="n">
+        <v>4.49893</v>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="n">
+        <v>1.48107</v>
+      </c>
+      <c r="AA80" s="2" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="AB80" s="2" t="n">
+        <v>1.24858</v>
+      </c>
+      <c r="AC80" s="2" t="n">
+        <v>14.208</v>
+      </c>
+      <c r="AD80" s="2" t="n">
+        <v>0.91549</v>
+      </c>
+      <c r="AE80" s="2" t="n">
+        <v>1.01408</v>
+      </c>
     </row>
     <row r="81">
-      <c r="E81" s="3" t="n">
+      <c r="E81" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F81" s="2" t="n">
         <v>5.64218</v>
       </c>
-      <c r="G81" s="3" t="n">
+      <c r="G81" s="2" t="n">
         <v>6.24152</v>
       </c>
-      <c r="H81" s="3" t="n">
+      <c r="H81" s="2" t="n">
         <v>4.5398</v>
       </c>
-      <c r="I81" s="3" t="n">
+      <c r="I81" s="2" t="n">
         <v>4.63838</v>
       </c>
-      <c r="J81" s="3" t="n">
+      <c r="J81" s="2" t="n">
         <v>3.4174</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="K81" s="2" t="n">
         <v>4.88161</v>
       </c>
+      <c r="O81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>6.35376</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>3.46102</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>8.40225</v>
+      </c>
+      <c r="S81" s="2" t="n">
+        <v>5.19398</v>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>3.13939</v>
+      </c>
+      <c r="U81" s="2" t="n">
+        <v>4.82217</v>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="n">
+        <v>3.3188</v>
+      </c>
+      <c r="AA81" s="2" t="n">
+        <v>2.11657</v>
+      </c>
+      <c r="AB81" s="2" t="n">
+        <v>2.38242</v>
+      </c>
+      <c r="AC81" s="2" t="n">
+        <v>12.50286</v>
+      </c>
+      <c r="AD81" s="2" t="n">
+        <v>1.72487</v>
+      </c>
+      <c r="AE81" s="2" t="n">
+        <v>2.24107</v>
+      </c>
     </row>
     <row r="82">
-      <c r="E82" s="3" t="n">
+      <c r="E82" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="F82" s="2" t="n">
         <v>5.83259</v>
       </c>
-      <c r="G82" s="3" t="n">
+      <c r="G82" s="2" t="n">
         <v>5.67627</v>
       </c>
-      <c r="H82" s="3" t="n">
+      <c r="H82" s="2" t="n">
         <v>4.46957</v>
       </c>
-      <c r="I82" s="3" t="n">
+      <c r="I82" s="2" t="n">
         <v>4.67463</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="J82" s="2" t="n">
         <v>3.3086</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" s="2" t="n">
         <v>4.82279</v>
       </c>
+      <c r="O82" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>6.57165</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>3.54159</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>8.477690000000001</v>
+      </c>
+      <c r="S82" s="2" t="n">
+        <v>5.47827</v>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>3.21765</v>
+      </c>
+      <c r="U82" s="2" t="n">
+        <v>4.94652</v>
+      </c>
+      <c r="X82" s="2" t="n"/>
+      <c r="Y82" s="2" t="n"/>
+      <c r="Z82" s="2" t="n"/>
+      <c r="AA82" s="2" t="n"/>
+      <c r="AB82" s="2" t="n"/>
+      <c r="AC82" s="2" t="n"/>
+      <c r="AD82" s="2" t="n"/>
+      <c r="AE82" s="2" t="n"/>
     </row>
     <row r="83">
-      <c r="E83" s="3" t="n">
+      <c r="E83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F83" s="3" t="n">
+      <c r="F83" s="2" t="n">
         <v>5.48806</v>
       </c>
-      <c r="G83" s="3" t="n">
+      <c r="G83" s="2" t="n">
         <v>5.30967</v>
       </c>
-      <c r="H83" s="3" t="n">
+      <c r="H83" s="2" t="n">
         <v>4.19472</v>
       </c>
-      <c r="I83" s="3" t="n">
+      <c r="I83" s="2" t="n">
         <v>4.41523</v>
       </c>
-      <c r="J83" s="3" t="n">
+      <c r="J83" s="2" t="n">
         <v>2.99933</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="K83" s="2" t="n">
         <v>4.45001</v>
       </c>
+      <c r="O83" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>6.72236</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>3.56998</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>8.588850000000001</v>
+      </c>
+      <c r="S83" s="2" t="n">
+        <v>5.58372</v>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>3.33653</v>
+      </c>
+      <c r="U83" s="2" t="n">
+        <v>5.1243</v>
+      </c>
+      <c r="X83" s="5" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="n">
+        <v>2.02383</v>
+      </c>
+      <c r="AA83" s="2" t="n">
+        <v>1.17439</v>
+      </c>
+      <c r="AB83" s="2" t="n">
+        <v>1.32727</v>
+      </c>
+      <c r="AC83" s="2" t="n">
+        <v>1.85022</v>
+      </c>
+      <c r="AD83" s="2" t="n">
+        <v>1.48436</v>
+      </c>
+      <c r="AE83" s="2" t="n">
+        <v>1.40337</v>
+      </c>
     </row>
     <row r="84">
-      <c r="E84" s="3" t="n">
+      <c r="E84" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="F84" s="2" t="n">
         <v>4.85567</v>
       </c>
-      <c r="G84" s="3" t="n">
+      <c r="G84" s="2" t="n">
         <v>5.0115</v>
       </c>
-      <c r="H84" s="3" t="n">
+      <c r="H84" s="2" t="n">
         <v>3.79124</v>
       </c>
-      <c r="I84" s="3" t="n">
+      <c r="I84" s="2" t="n">
         <v>4.00274</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="J84" s="2" t="n">
         <v>2.60281</v>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="K84" s="2" t="n">
         <v>4.09592</v>
       </c>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="n"/>
+      <c r="Q84" s="2" t="n"/>
+      <c r="R84" s="2" t="n"/>
+      <c r="S84" s="2" t="n"/>
+      <c r="T84" s="2" t="n"/>
+      <c r="U84" s="2" t="n"/>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="n">
+        <v>2.02093</v>
+      </c>
+      <c r="AA84" s="2" t="n">
+        <v>1.75854</v>
+      </c>
+      <c r="AB84" s="2" t="n">
+        <v>1.51906</v>
+      </c>
+      <c r="AC84" s="2" t="n">
+        <v>2.13297</v>
+      </c>
+      <c r="AD84" s="2" t="n">
+        <v>8.475899999999999</v>
+      </c>
+      <c r="AE84" s="2" t="n">
+        <v>1.50086</v>
+      </c>
     </row>
     <row r="85">
-      <c r="E85" s="3" t="n">
+      <c r="E85" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F85" s="3" t="n">
+      <c r="F85" s="2" t="n">
         <v>4.16081</v>
       </c>
-      <c r="G85" s="3" t="n">
+      <c r="G85" s="2" t="n">
         <v>4.72852</v>
       </c>
-      <c r="H85" s="3" t="n">
+      <c r="H85" s="2" t="n">
         <v>3.27898</v>
       </c>
-      <c r="I85" s="3" t="n">
+      <c r="I85" s="2" t="n">
         <v>3.54386</v>
       </c>
-      <c r="J85" s="3" t="n">
+      <c r="J85" s="2" t="n">
         <v>2.27349</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="K85" s="2" t="n">
         <v>3.42237</v>
       </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>DenseNet-BC-40</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>3.3188</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>2.11657</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>2.38242</v>
+      </c>
+      <c r="S85" s="2" t="n">
+        <v>12.50286</v>
+      </c>
+      <c r="T85" s="2" t="n">
+        <v>1.72487</v>
+      </c>
+      <c r="U85" s="2" t="n">
+        <v>2.24107</v>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="n">
+        <v>3.49242</v>
+      </c>
+      <c r="AA85" s="2" t="n">
+        <v>2.45597</v>
+      </c>
+      <c r="AB85" s="2" t="n">
+        <v>2.45505</v>
+      </c>
+      <c r="AC85" s="2" t="n">
+        <v>3.04778</v>
+      </c>
+      <c r="AD85" s="2" t="n">
+        <v>7.06688</v>
+      </c>
+      <c r="AE85" s="2" t="n">
+        <v>2.72461</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="O86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>4.59611</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>2.42815</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>3.67429</v>
+      </c>
+      <c r="S86" s="2" t="n">
+        <v>7.84998</v>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>2.40956</v>
+      </c>
+      <c r="U86" s="2" t="n">
+        <v>3.25457</v>
+      </c>
+      <c r="X86" s="2" t="n"/>
+      <c r="Y86" s="2" t="n"/>
+      <c r="Z86" s="2" t="n"/>
+      <c r="AA86" s="2" t="n"/>
+      <c r="AB86" s="2" t="n"/>
+      <c r="AC86" s="2" t="n"/>
+      <c r="AD86" s="2" t="n"/>
+      <c r="AE86" s="2" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>SE-ResNet-20</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F87" s="3" t="n">
+      <c r="F87" s="2" t="n">
         <v>4.43778</v>
       </c>
-      <c r="G87" s="3" t="n">
+      <c r="G87" s="2" t="n">
         <v>2.68155</v>
       </c>
-      <c r="H87" s="3" t="n">
+      <c r="H87" s="2" t="n">
         <v>12.39732</v>
       </c>
-      <c r="I87" s="3" t="n">
+      <c r="I87" s="2" t="n">
         <v>3.80847</v>
       </c>
-      <c r="J87" s="3" t="n">
+      <c r="J87" s="2" t="n">
         <v>2.39275</v>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="K87" s="2" t="n">
         <v>3.38826</v>
       </c>
+      <c r="O87" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>5.27228</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>2.73085</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>4.01116</v>
+      </c>
+      <c r="S87" s="2" t="n">
+        <v>8.23044</v>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>2.56256</v>
+      </c>
+      <c r="U87" s="2" t="n">
+        <v>3.72818</v>
+      </c>
+      <c r="X87" s="5" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>FGSM</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="n">
+        <v>1.78847</v>
+      </c>
+      <c r="AA87" s="2" t="n">
+        <v>1.08325</v>
+      </c>
+      <c r="AB87" s="2" t="n">
+        <v>1.25119</v>
+      </c>
+      <c r="AC87" s="2" t="n">
+        <v>1.64322</v>
+      </c>
+      <c r="AD87" s="2" t="n">
+        <v>1.10551</v>
+      </c>
+      <c r="AE87" s="2" t="n">
+        <v>1.75323</v>
+      </c>
     </row>
     <row r="88">
-      <c r="E88" s="3" t="n">
+      <c r="E88" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F88" s="3" t="n">
+      <c r="F88" s="2" t="n">
         <v>5.41744</v>
       </c>
-      <c r="G88" s="3" t="n">
+      <c r="G88" s="2" t="n">
         <v>3.12383</v>
       </c>
-      <c r="H88" s="3" t="n">
+      <c r="H88" s="2" t="n">
         <v>11.94849</v>
       </c>
-      <c r="I88" s="3" t="n">
+      <c r="I88" s="2" t="n">
         <v>4.54404</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="J88" s="2" t="n">
         <v>2.75929</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="K88" s="2" t="n">
         <v>4.11948</v>
       </c>
+      <c r="O88" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>2.82703</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>4.24908</v>
+      </c>
+      <c r="S88" s="2" t="n">
+        <v>8.27887</v>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>2.71907</v>
+      </c>
+      <c r="U88" s="2" t="n">
+        <v>3.85549</v>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>IFGSM</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="n">
+        <v>2.53037</v>
+      </c>
+      <c r="AA88" s="2" t="n">
+        <v>2.07779</v>
+      </c>
+      <c r="AB88" s="2" t="n">
+        <v>1.86417</v>
+      </c>
+      <c r="AC88" s="2" t="n">
+        <v>2.18284</v>
+      </c>
+      <c r="AD88" s="2" t="n">
+        <v>1.64255</v>
+      </c>
+      <c r="AE88" s="2" t="n">
+        <v>9.11659</v>
+      </c>
     </row>
     <row r="89">
-      <c r="E89" s="3" t="n">
+      <c r="E89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="3" t="n">
+      <c r="F89" s="2" t="n">
         <v>6.09906</v>
       </c>
-      <c r="G89" s="3" t="n">
+      <c r="G89" s="2" t="n">
         <v>3.48682</v>
       </c>
-      <c r="H89" s="3" t="n">
+      <c r="H89" s="2" t="n">
         <v>10.33462</v>
       </c>
-      <c r="I89" s="3" t="n">
+      <c r="I89" s="2" t="n">
         <v>5.13824</v>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="J89" s="2" t="n">
         <v>3.07726</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="K89" s="2" t="n">
         <v>4.63591</v>
       </c>
+      <c r="O89" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>5.60979</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>2.81328</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>4.25741</v>
+      </c>
+      <c r="S89" s="2" t="n">
+        <v>8.399789999999999</v>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>2.74096</v>
+      </c>
+      <c r="U89" s="2" t="n">
+        <v>3.94633</v>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>MIFGSM</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="n">
+        <v>3.25545</v>
+      </c>
+      <c r="AA89" s="2" t="n">
+        <v>2.40469</v>
+      </c>
+      <c r="AB89" s="2" t="n">
+        <v>2.30561</v>
+      </c>
+      <c r="AC89" s="2" t="n">
+        <v>2.59116</v>
+      </c>
+      <c r="AD89" s="2" t="n">
+        <v>2.06655</v>
+      </c>
+      <c r="AE89" s="2" t="n">
+        <v>7.09179</v>
+      </c>
     </row>
     <row r="90">
-      <c r="E90" s="3" t="n">
+      <c r="E90" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="F90" s="2" t="n">
         <v>6.43411</v>
       </c>
-      <c r="G90" s="3" t="n">
+      <c r="G90" s="2" t="n">
         <v>3.57374</v>
       </c>
-      <c r="H90" s="3" t="n">
+      <c r="H90" s="2" t="n">
         <v>9.13749</v>
       </c>
-      <c r="I90" s="3" t="n">
+      <c r="I90" s="2" t="n">
         <v>5.21115</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="J90" s="2" t="n">
         <v>3.21733</v>
       </c>
-      <c r="K90" s="3" t="n">
+      <c r="K90" s="2" t="n">
         <v>4.99159</v>
       </c>
+      <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="n"/>
+      <c r="P90" s="2" t="n"/>
+      <c r="Q90" s="2" t="n"/>
+      <c r="R90" s="2" t="n"/>
+      <c r="S90" s="2" t="n"/>
+      <c r="T90" s="2" t="n"/>
+      <c r="U90" s="2" t="n"/>
+      <c r="X90" s="2" t="n"/>
+      <c r="Y90" s="2" t="n"/>
+      <c r="Z90" s="2" t="n"/>
+      <c r="AA90" s="2" t="n"/>
+      <c r="AB90" s="2" t="n"/>
+      <c r="AC90" s="2" t="n"/>
+      <c r="AD90" s="2" t="n"/>
+      <c r="AE90" s="2" t="n"/>
     </row>
     <row r="91">
-      <c r="E91" s="3" t="n">
+      <c r="E91" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="F91" s="2" t="n">
         <v>6.18764</v>
       </c>
-      <c r="G91" s="3" t="n">
+      <c r="G91" s="2" t="n">
         <v>3.35431</v>
       </c>
-      <c r="H91" s="3" t="n">
+      <c r="H91" s="2" t="n">
         <v>8.50858</v>
       </c>
-      <c r="I91" s="3" t="n">
+      <c r="I91" s="2" t="n">
         <v>5.11119</v>
       </c>
-      <c r="J91" s="3" t="n">
+      <c r="J91" s="2" t="n">
         <v>3.06766</v>
       </c>
-      <c r="K91" s="3" t="n">
+      <c r="K91" s="2" t="n">
         <v>4.70662</v>
       </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>RoR-3-110</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>3.49242</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>2.45597</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>2.45505</v>
+      </c>
+      <c r="S91" s="2" t="n">
+        <v>3.04778</v>
+      </c>
+      <c r="T91" s="2" t="n">
+        <v>7.06688</v>
+      </c>
+      <c r="U91" s="2" t="n">
+        <v>2.72461</v>
+      </c>
+      <c r="X91" s="2" t="n"/>
+      <c r="Y91" s="2" t="n"/>
+      <c r="Z91" s="2" t="n"/>
+      <c r="AA91" s="2" t="n"/>
+      <c r="AB91" s="2" t="n"/>
+      <c r="AC91" s="2" t="n"/>
+      <c r="AD91" s="2" t="n"/>
+      <c r="AE91" s="2" t="n"/>
     </row>
     <row r="92">
-      <c r="E92" s="3" t="n">
+      <c r="E92" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="F92" s="2" t="n">
         <v>5.96045</v>
       </c>
-      <c r="G92" s="3" t="n">
+      <c r="G92" s="2" t="n">
         <v>3.22363</v>
       </c>
-      <c r="H92" s="3" t="n">
+      <c r="H92" s="2" t="n">
         <v>8.05494</v>
       </c>
-      <c r="I92" s="3" t="n">
+      <c r="I92" s="2" t="n">
         <v>4.9347</v>
       </c>
-      <c r="J92" s="3" t="n">
+      <c r="J92" s="2" t="n">
         <v>2.83232</v>
       </c>
-      <c r="K92" s="3" t="n">
+      <c r="K92" s="2" t="n">
         <v>4.49893</v>
       </c>
+      <c r="O92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>5.215</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>3.02471</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>3.89843</v>
+      </c>
+      <c r="S92" s="2" t="n">
+        <v>4.05517</v>
+      </c>
+      <c r="T92" s="2" t="n">
+        <v>4.30283</v>
+      </c>
+      <c r="U92" s="2" t="n">
+        <v>4.20544</v>
+      </c>
+      <c r="X92" s="2" t="n"/>
+      <c r="Y92" s="2" t="n"/>
+      <c r="Z92" s="2" t="n"/>
+      <c r="AA92" s="2" t="n"/>
+      <c r="AB92" s="2" t="n"/>
+      <c r="AC92" s="2" t="n"/>
+      <c r="AD92" s="2" t="n"/>
+      <c r="AE92" s="2" t="n"/>
     </row>
     <row r="93">
-      <c r="E93" s="3" t="n">
+      <c r="E93" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F93" s="3" t="n">
+      <c r="F93" s="2" t="n">
         <v>5.53402</v>
       </c>
-      <c r="G93" s="3" t="n">
+      <c r="G93" s="2" t="n">
         <v>2.91705</v>
       </c>
-      <c r="H93" s="3" t="n">
+      <c r="H93" s="2" t="n">
         <v>7.75801</v>
       </c>
-      <c r="I93" s="3" t="n">
+      <c r="I93" s="2" t="n">
         <v>4.62243</v>
       </c>
-      <c r="J93" s="3" t="n">
+      <c r="J93" s="2" t="n">
         <v>2.54868</v>
       </c>
-      <c r="K93" s="3" t="n">
+      <c r="K93" s="2" t="n">
         <v>4.07519</v>
       </c>
+      <c r="O93" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>5.55047</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>3.3374</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>4.2759</v>
+      </c>
+      <c r="S93" s="2" t="n">
+        <v>4.42637</v>
+      </c>
+      <c r="T93" s="2" t="n">
+        <v>4.7344</v>
+      </c>
+      <c r="U93" s="2" t="n">
+        <v>4.60573</v>
+      </c>
+      <c r="X93" s="2" t="n"/>
+      <c r="Y93" s="2" t="n"/>
+      <c r="Z93" s="2" t="n"/>
+      <c r="AA93" s="2" t="n"/>
+      <c r="AB93" s="2" t="n"/>
+      <c r="AC93" s="2" t="n"/>
+      <c r="AD93" s="2" t="n"/>
+      <c r="AE93" s="2" t="n"/>
     </row>
     <row r="94">
-      <c r="E94" s="3" t="n">
+      <c r="E94" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="F94" s="2" t="n">
         <v>5.02015</v>
       </c>
-      <c r="G94" s="3" t="n">
+      <c r="G94" s="2" t="n">
         <v>2.65018</v>
       </c>
-      <c r="H94" s="3" t="n">
+      <c r="H94" s="2" t="n">
         <v>7.48808</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I94" s="2" t="n">
         <v>4.3855</v>
       </c>
-      <c r="J94" s="3" t="n">
+      <c r="J94" s="2" t="n">
         <v>2.25553</v>
       </c>
-      <c r="K94" s="3" t="n">
+      <c r="K94" s="2" t="n">
         <v>3.67838</v>
       </c>
+      <c r="O94" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>5.72591</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>3.44509</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>4.35129</v>
+      </c>
+      <c r="S94" s="2" t="n">
+        <v>4.54393</v>
+      </c>
+      <c r="T94" s="2" t="n">
+        <v>4.86326</v>
+      </c>
+      <c r="U94" s="2" t="n">
+        <v>4.86168</v>
+      </c>
+      <c r="X94" s="2" t="n"/>
+      <c r="Y94" s="2" t="n"/>
+      <c r="Z94" s="2" t="n"/>
+      <c r="AA94" s="2" t="n"/>
+      <c r="AB94" s="2" t="n"/>
+      <c r="AC94" s="2" t="n"/>
+      <c r="AD94" s="2" t="n"/>
+      <c r="AE94" s="2" t="n"/>
     </row>
     <row r="95">
-      <c r="E95" s="3" t="n">
+      <c r="E95" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="F95" s="2" t="n">
         <v>4.2279</v>
       </c>
-      <c r="G95" s="3" t="n">
+      <c r="G95" s="2" t="n">
         <v>2.39785</v>
       </c>
-      <c r="H95" s="3" t="n">
+      <c r="H95" s="2" t="n">
         <v>7.15877</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I95" s="2" t="n">
         <v>3.86667</v>
       </c>
-      <c r="J95" s="3" t="n">
+      <c r="J95" s="2" t="n">
         <v>1.97705</v>
       </c>
-      <c r="K95" s="3" t="n">
+      <c r="K95" s="2" t="n">
         <v>3.16152</v>
       </c>
+      <c r="O95" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>5.89913</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>3.62211</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>4.47407</v>
+      </c>
+      <c r="S95" s="2" t="n">
+        <v>4.66677</v>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>5.00008</v>
+      </c>
+      <c r="U95" s="2" t="n">
+        <v>4.80032</v>
+      </c>
+      <c r="X95" s="2" t="n"/>
+      <c r="Y95" s="2" t="n"/>
+      <c r="Z95" s="2" t="n"/>
+      <c r="AA95" s="2" t="n"/>
+      <c r="AB95" s="2" t="n"/>
+      <c r="AC95" s="2" t="n"/>
+      <c r="AD95" s="2" t="n"/>
+      <c r="AE95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="n"/>
+      <c r="P96" s="2" t="n"/>
+      <c r="Q96" s="2" t="n"/>
+      <c r="R96" s="2" t="n"/>
+      <c r="S96" s="2" t="n"/>
+      <c r="T96" s="2" t="n"/>
+      <c r="U96" s="2" t="n"/>
+      <c r="X96" s="2" t="n"/>
+      <c r="Y96" s="2" t="n"/>
+      <c r="Z96" s="2" t="n"/>
+      <c r="AA96" s="2" t="n"/>
+      <c r="AB96" s="2" t="n"/>
+      <c r="AC96" s="2" t="n"/>
+      <c r="AD96" s="2" t="n"/>
+      <c r="AE96" s="2" t="n"/>
     </row>
     <row r="97">
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>DenseNet-BC-40</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="F97" s="2" t="n">
         <v>3.3188</v>
       </c>
-      <c r="G97" s="3" t="n">
+      <c r="G97" s="2" t="n">
         <v>2.11657</v>
       </c>
-      <c r="H97" s="3" t="n">
+      <c r="H97" s="2" t="n">
         <v>2.38242</v>
       </c>
-      <c r="I97" s="3" t="n">
+      <c r="I97" s="2" t="n">
         <v>12.50286</v>
       </c>
-      <c r="J97" s="3" t="n">
+      <c r="J97" s="2" t="n">
         <v>1.72487</v>
       </c>
-      <c r="K97" s="3" t="n">
+      <c r="K97" s="2" t="n">
         <v>2.24107</v>
       </c>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>DIA-PreResNet-56</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>3.25545</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>2.40469</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>2.30561</v>
+      </c>
+      <c r="S97" s="2" t="n">
+        <v>2.59116</v>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>2.06655</v>
+      </c>
+      <c r="U97" s="2" t="n">
+        <v>7.09179</v>
+      </c>
+      <c r="X97" s="2" t="n"/>
+      <c r="Y97" s="2" t="n"/>
+      <c r="Z97" s="2" t="n"/>
+      <c r="AA97" s="2" t="n"/>
+      <c r="AB97" s="2" t="n"/>
+      <c r="AC97" s="2" t="n"/>
+      <c r="AD97" s="2" t="n"/>
+      <c r="AE97" s="2" t="n"/>
     </row>
     <row r="98">
-      <c r="E98" s="3" t="n">
+      <c r="E98" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F98" s="3" t="n">
+      <c r="F98" s="2" t="n">
         <v>4.2457</v>
       </c>
-      <c r="G98" s="3" t="n">
+      <c r="G98" s="2" t="n">
         <v>2.57025</v>
       </c>
-      <c r="H98" s="3" t="n">
+      <c r="H98" s="2" t="n">
         <v>3.22984</v>
       </c>
-      <c r="I98" s="3" t="n">
+      <c r="I98" s="2" t="n">
         <v>11.71959</v>
       </c>
-      <c r="J98" s="3" t="n">
+      <c r="J98" s="2" t="n">
         <v>2.23699</v>
       </c>
-      <c r="K98" s="3" t="n">
+      <c r="K98" s="2" t="n">
         <v>3.02985</v>
       </c>
+      <c r="O98" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>5.40266</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>3.1888</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>4.0229</v>
+      </c>
+      <c r="S98" s="2" t="n">
+        <v>3.90637</v>
+      </c>
+      <c r="T98" s="2" t="n">
+        <v>2.93938</v>
+      </c>
+      <c r="U98" s="2" t="n">
+        <v>6.43327</v>
+      </c>
+      <c r="X98" s="2" t="n"/>
+      <c r="Y98" s="2" t="n"/>
+      <c r="Z98" s="2" t="n"/>
+      <c r="AA98" s="2" t="n"/>
+      <c r="AB98" s="2" t="n"/>
+      <c r="AC98" s="2" t="n"/>
+      <c r="AD98" s="2" t="n"/>
+      <c r="AE98" s="2" t="n"/>
     </row>
     <row r="99">
-      <c r="E99" s="3" t="n">
+      <c r="E99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="3" t="n">
+      <c r="F99" s="2" t="n">
         <v>4.7004</v>
       </c>
-      <c r="G99" s="3" t="n">
+      <c r="G99" s="2" t="n">
         <v>2.82025</v>
       </c>
-      <c r="H99" s="3" t="n">
+      <c r="H99" s="2" t="n">
         <v>3.63166</v>
       </c>
-      <c r="I99" s="3" t="n">
+      <c r="I99" s="2" t="n">
         <v>10.07037</v>
       </c>
-      <c r="J99" s="3" t="n">
+      <c r="J99" s="2" t="n">
         <v>2.56895</v>
       </c>
-      <c r="K99" s="3" t="n">
+      <c r="K99" s="2" t="n">
         <v>3.44993</v>
       </c>
+      <c r="O99" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>5.6447</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>3.31765</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>4.32127</v>
+      </c>
+      <c r="S99" s="2" t="n">
+        <v>4.33394</v>
+      </c>
+      <c r="T99" s="2" t="n">
+        <v>3.07719</v>
+      </c>
+      <c r="U99" s="2" t="n">
+        <v>6.77042</v>
+      </c>
+      <c r="X99" s="2" t="n"/>
+      <c r="Y99" s="2" t="n"/>
+      <c r="Z99" s="2" t="n"/>
+      <c r="AA99" s="2" t="n"/>
+      <c r="AB99" s="2" t="n"/>
+      <c r="AC99" s="2" t="n"/>
+      <c r="AD99" s="2" t="n"/>
+      <c r="AE99" s="2" t="n"/>
     </row>
     <row r="100">
-      <c r="E100" s="3" t="n">
+      <c r="E100" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F100" s="3" t="n">
+      <c r="F100" s="2" t="n">
         <v>5.17196</v>
       </c>
-      <c r="G100" s="3" t="n">
+      <c r="G100" s="2" t="n">
         <v>2.87551</v>
       </c>
-      <c r="H100" s="3" t="n">
+      <c r="H100" s="2" t="n">
         <v>4.07888</v>
       </c>
-      <c r="I100" s="3" t="n">
+      <c r="I100" s="2" t="n">
         <v>8.802149999999999</v>
       </c>
-      <c r="J100" s="3" t="n">
+      <c r="J100" s="2" t="n">
         <v>2.68939</v>
       </c>
-      <c r="K100" s="3" t="n">
+      <c r="K100" s="2" t="n">
         <v>3.79773</v>
       </c>
+      <c r="O100" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>5.81914</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>3.4445</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>4.48971</v>
+      </c>
+      <c r="S100" s="2" t="n">
+        <v>4.53647</v>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>3.20024</v>
+      </c>
+      <c r="U100" s="2" t="n">
+        <v>7.05946</v>
+      </c>
+      <c r="X100" s="2" t="n"/>
+      <c r="Y100" s="2" t="n"/>
+      <c r="Z100" s="2" t="n"/>
+      <c r="AA100" s="2" t="n"/>
+      <c r="AB100" s="2" t="n"/>
+      <c r="AC100" s="2" t="n"/>
+      <c r="AD100" s="2" t="n"/>
+      <c r="AE100" s="2" t="n"/>
     </row>
     <row r="101">
-      <c r="E101" s="3" t="n">
+      <c r="E101" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F101" s="3" t="n">
+      <c r="F101" s="2" t="n">
         <v>5.20782</v>
       </c>
-      <c r="G101" s="3" t="n">
+      <c r="G101" s="2" t="n">
         <v>2.73591</v>
       </c>
-      <c r="H101" s="3" t="n">
+      <c r="H101" s="2" t="n">
         <v>3.98449</v>
       </c>
-      <c r="I101" s="3" t="n">
+      <c r="I101" s="2" t="n">
         <v>8.07826</v>
       </c>
-      <c r="J101" s="3" t="n">
+      <c r="J101" s="2" t="n">
         <v>2.56269</v>
       </c>
-      <c r="K101" s="3" t="n">
+      <c r="K101" s="2" t="n">
         <v>3.50999</v>
       </c>
+      <c r="O101" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>5.82488</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>3.49115</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>4.50219</v>
+      </c>
+      <c r="S101" s="2" t="n">
+        <v>4.48826</v>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>3.24107</v>
+      </c>
+      <c r="U101" s="2" t="n">
+        <v>7.01131</v>
+      </c>
+      <c r="X101" s="2" t="n"/>
+      <c r="Y101" s="2" t="n"/>
+      <c r="Z101" s="2" t="n"/>
+      <c r="AA101" s="2" t="n"/>
+      <c r="AB101" s="2" t="n"/>
+      <c r="AC101" s="2" t="n"/>
+      <c r="AD101" s="2" t="n"/>
+      <c r="AE101" s="2" t="n"/>
     </row>
     <row r="102">
-      <c r="E102" s="3" t="n">
+      <c r="E102" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F102" s="3" t="n">
+      <c r="F102" s="2" t="n">
         <v>4.59611</v>
       </c>
-      <c r="G102" s="3" t="n">
+      <c r="G102" s="2" t="n">
         <v>2.42815</v>
       </c>
-      <c r="H102" s="3" t="n">
+      <c r="H102" s="2" t="n">
         <v>3.67429</v>
       </c>
-      <c r="I102" s="3" t="n">
+      <c r="I102" s="2" t="n">
         <v>7.84998</v>
       </c>
-      <c r="J102" s="3" t="n">
+      <c r="J102" s="2" t="n">
         <v>2.40956</v>
       </c>
-      <c r="K102" s="3" t="n">
+      <c r="K102" s="2" t="n">
         <v>3.25457</v>
       </c>
+      <c r="N102" s="2" t="n"/>
+      <c r="O102" s="2" t="n"/>
+      <c r="P102" s="2" t="n"/>
+      <c r="Q102" s="2" t="n"/>
+      <c r="R102" s="2" t="n"/>
+      <c r="S102" s="2" t="n"/>
+      <c r="T102" s="2" t="n"/>
+      <c r="U102" s="2" t="n"/>
+      <c r="X102" s="2" t="n"/>
+      <c r="Y102" s="2" t="n"/>
+      <c r="Z102" s="2" t="n"/>
+      <c r="AA102" s="2" t="n"/>
+      <c r="AB102" s="2" t="n"/>
+      <c r="AC102" s="2" t="n"/>
+      <c r="AD102" s="2" t="n"/>
+      <c r="AE102" s="2" t="n"/>
     </row>
     <row r="103">
-      <c r="E103" s="3" t="n">
+      <c r="E103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F103" s="3" t="n">
+      <c r="F103" s="2" t="n">
         <v>3.78133</v>
       </c>
-      <c r="G103" s="3" t="n">
+      <c r="G103" s="2" t="n">
         <v>1.99764</v>
       </c>
-      <c r="H103" s="3" t="n">
+      <c r="H103" s="2" t="n">
         <v>2.91753</v>
       </c>
-      <c r="I103" s="3" t="n">
+      <c r="I103" s="2" t="n">
         <v>7.69562</v>
       </c>
-      <c r="J103" s="3" t="n">
+      <c r="J103" s="2" t="n">
         <v>1.99797</v>
       </c>
-      <c r="K103" s="3" t="n">
+      <c r="K103" s="2" t="n">
         <v>2.7406</v>
       </c>
+      <c r="N103" s="2" t="n"/>
+      <c r="O103" s="2" t="n"/>
+      <c r="P103" s="2" t="n"/>
+      <c r="Q103" s="2" t="n"/>
+      <c r="R103" s="2" t="n"/>
+      <c r="S103" s="2" t="n"/>
+      <c r="T103" s="2" t="n"/>
+      <c r="U103" s="2" t="n"/>
+      <c r="X103" s="2" t="n"/>
+      <c r="Y103" s="2" t="n"/>
+      <c r="Z103" s="2" t="n"/>
+      <c r="AA103" s="2" t="n"/>
+      <c r="AB103" s="2" t="n"/>
+      <c r="AC103" s="2" t="n"/>
+      <c r="AD103" s="2" t="n"/>
+      <c r="AE103" s="2" t="n"/>
     </row>
     <row r="104">
-      <c r="E104" s="3" t="n">
+      <c r="E104" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F104" s="3" t="n">
+      <c r="F104" s="2" t="n">
         <v>2.69167</v>
       </c>
-      <c r="G104" s="3" t="n">
+      <c r="G104" s="2" t="n">
         <v>1.57072</v>
       </c>
-      <c r="H104" s="3" t="n">
+      <c r="H104" s="2" t="n">
         <v>2.2805</v>
       </c>
-      <c r="I104" s="3" t="n">
+      <c r="I104" s="2" t="n">
         <v>7.40605</v>
       </c>
-      <c r="J104" s="3" t="n">
+      <c r="J104" s="2" t="n">
         <v>1.43429</v>
       </c>
-      <c r="K104" s="3" t="n">
+      <c r="K104" s="2" t="n">
         <v>2.0703</v>
       </c>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="2" t="n"/>
+      <c r="P104" s="2" t="n"/>
+      <c r="Q104" s="2" t="n"/>
+      <c r="R104" s="2" t="n"/>
+      <c r="S104" s="2" t="n"/>
+      <c r="T104" s="2" t="n"/>
+      <c r="U104" s="2" t="n"/>
+      <c r="X104" s="2" t="n"/>
+      <c r="Y104" s="2" t="n"/>
+      <c r="Z104" s="2" t="n"/>
+      <c r="AA104" s="2" t="n"/>
+      <c r="AB104" s="2" t="n"/>
+      <c r="AC104" s="2" t="n"/>
+      <c r="AD104" s="2" t="n"/>
+      <c r="AE104" s="2" t="n"/>
     </row>
     <row r="105">
-      <c r="E105" s="3" t="n">
+      <c r="E105" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F105" s="3" t="n">
+      <c r="F105" s="2" t="n">
         <v>2.03654</v>
       </c>
-      <c r="G105" s="3" t="n">
+      <c r="G105" s="2" t="n">
         <v>1.26738</v>
       </c>
-      <c r="H105" s="3" t="n">
+      <c r="H105" s="2" t="n">
         <v>1.71211</v>
       </c>
-      <c r="I105" s="3" t="n">
+      <c r="I105" s="2" t="n">
         <v>7.0514</v>
       </c>
-      <c r="J105" s="3" t="n">
+      <c r="J105" s="2" t="n">
         <v>1.16237</v>
       </c>
-      <c r="K105" s="3" t="n">
+      <c r="K105" s="2" t="n">
         <v>1.57665</v>
       </c>
+      <c r="N105" s="2" t="n"/>
+      <c r="O105" s="2" t="n"/>
+      <c r="P105" s="2" t="n"/>
+      <c r="Q105" s="2" t="n"/>
+      <c r="R105" s="2" t="n"/>
+      <c r="S105" s="2" t="n"/>
+      <c r="T105" s="2" t="n"/>
+      <c r="U105" s="2" t="n"/>
+      <c r="X105" s="2" t="n"/>
+      <c r="Y105" s="2" t="n"/>
+      <c r="Z105" s="2" t="n"/>
+      <c r="AA105" s="2" t="n"/>
+      <c r="AB105" s="2" t="n"/>
+      <c r="AC105" s="2" t="n"/>
+      <c r="AD105" s="2" t="n"/>
+      <c r="AE105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="2" t="n"/>
+      <c r="P106" s="2" t="n"/>
+      <c r="Q106" s="2" t="n"/>
+      <c r="R106" s="2" t="n"/>
+      <c r="S106" s="2" t="n"/>
+      <c r="T106" s="2" t="n"/>
+      <c r="U106" s="2" t="n"/>
+      <c r="X106" s="2" t="n"/>
+      <c r="Y106" s="2" t="n"/>
+      <c r="Z106" s="2" t="n"/>
+      <c r="AA106" s="2" t="n"/>
+      <c r="AB106" s="2" t="n"/>
+      <c r="AC106" s="2" t="n"/>
+      <c r="AD106" s="2" t="n"/>
+      <c r="AE106" s="2" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>RoR-3-110</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F107" s="3" t="n">
+      <c r="F107" s="2" t="n">
         <v>3.49242</v>
       </c>
-      <c r="G107" s="3" t="n">
+      <c r="G107" s="2" t="n">
         <v>2.45597</v>
       </c>
-      <c r="H107" s="3" t="n">
+      <c r="H107" s="2" t="n">
         <v>2.45505</v>
       </c>
-      <c r="I107" s="3" t="n">
+      <c r="I107" s="2" t="n">
         <v>3.04778</v>
       </c>
-      <c r="J107" s="3" t="n">
+      <c r="J107" s="2" t="n">
         <v>7.06688</v>
       </c>
-      <c r="K107" s="3" t="n">
+      <c r="K107" s="2" t="n">
         <v>2.72461</v>
       </c>
+      <c r="N107" s="2" t="n"/>
+      <c r="O107" s="2" t="n"/>
+      <c r="P107" s="2" t="n"/>
+      <c r="Q107" s="2" t="n"/>
+      <c r="R107" s="2" t="n"/>
+      <c r="S107" s="2" t="n"/>
+      <c r="T107" s="2" t="n"/>
+      <c r="U107" s="2" t="n"/>
+      <c r="X107" s="2" t="n"/>
+      <c r="Y107" s="2" t="n"/>
+      <c r="Z107" s="2" t="n"/>
+      <c r="AA107" s="2" t="n"/>
+      <c r="AB107" s="2" t="n"/>
+      <c r="AC107" s="2" t="n"/>
+      <c r="AD107" s="2" t="n"/>
+      <c r="AE107" s="2" t="n"/>
     </row>
     <row r="108">
-      <c r="E108" s="3" t="n">
+      <c r="E108" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F108" s="3" t="n">
+      <c r="F108" s="2" t="n">
         <v>3.77323</v>
       </c>
-      <c r="G108" s="3" t="n">
+      <c r="G108" s="2" t="n">
         <v>2.74622</v>
       </c>
-      <c r="H108" s="3" t="n">
+      <c r="H108" s="2" t="n">
         <v>2.74619</v>
       </c>
-      <c r="I108" s="3" t="n">
+      <c r="I108" s="2" t="n">
         <v>3.35825</v>
       </c>
-      <c r="J108" s="3" t="n">
+      <c r="J108" s="2" t="n">
         <v>6.34906</v>
       </c>
-      <c r="K108" s="3" t="n">
+      <c r="K108" s="2" t="n">
         <v>3.10186</v>
       </c>
+      <c r="N108" s="2" t="n"/>
+      <c r="O108" s="2" t="n"/>
+      <c r="P108" s="2" t="n"/>
+      <c r="Q108" s="2" t="n"/>
+      <c r="R108" s="2" t="n"/>
+      <c r="S108" s="2" t="n"/>
+      <c r="T108" s="2" t="n"/>
+      <c r="U108" s="2" t="n"/>
+      <c r="X108" s="2" t="n"/>
+      <c r="Y108" s="2" t="n"/>
+      <c r="Z108" s="2" t="n"/>
+      <c r="AA108" s="2" t="n"/>
+      <c r="AB108" s="2" t="n"/>
+      <c r="AC108" s="2" t="n"/>
+      <c r="AD108" s="2" t="n"/>
+      <c r="AE108" s="2" t="n"/>
     </row>
     <row r="109">
-      <c r="E109" s="3" t="n">
+      <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="3" t="n">
+      <c r="F109" s="2" t="n">
         <v>4.55179</v>
       </c>
-      <c r="G109" s="3" t="n">
+      <c r="G109" s="2" t="n">
         <v>3.1279</v>
       </c>
-      <c r="H109" s="3" t="n">
+      <c r="H109" s="2" t="n">
         <v>3.51447</v>
       </c>
-      <c r="I109" s="3" t="n">
+      <c r="I109" s="2" t="n">
         <v>3.90468</v>
       </c>
-      <c r="J109" s="3" t="n">
+      <c r="J109" s="2" t="n">
         <v>5.54531</v>
       </c>
-      <c r="K109" s="3" t="n">
+      <c r="K109" s="2" t="n">
         <v>3.67123</v>
       </c>
+      <c r="N109" s="2" t="n"/>
+      <c r="O109" s="2" t="n"/>
+      <c r="P109" s="2" t="n"/>
+      <c r="Q109" s="2" t="n"/>
+      <c r="R109" s="2" t="n"/>
+      <c r="S109" s="2" t="n"/>
+      <c r="T109" s="2" t="n"/>
+      <c r="U109" s="2" t="n"/>
+      <c r="X109" s="2" t="n"/>
+      <c r="Y109" s="2" t="n"/>
+      <c r="Z109" s="2" t="n"/>
+      <c r="AA109" s="2" t="n"/>
+      <c r="AB109" s="2" t="n"/>
+      <c r="AC109" s="2" t="n"/>
+      <c r="AD109" s="2" t="n"/>
+      <c r="AE109" s="2" t="n"/>
     </row>
     <row r="110">
-      <c r="E110" s="3" t="n">
+      <c r="E110" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F110" s="3" t="n">
+      <c r="F110" s="2" t="n">
         <v>4.66683</v>
       </c>
-      <c r="G110" s="3" t="n">
+      <c r="G110" s="2" t="n">
         <v>3.12799</v>
       </c>
-      <c r="H110" s="3" t="n">
+      <c r="H110" s="2" t="n">
         <v>3.68091</v>
       </c>
-      <c r="I110" s="3" t="n">
+      <c r="I110" s="2" t="n">
         <v>3.91165</v>
       </c>
-      <c r="J110" s="3" t="n">
+      <c r="J110" s="2" t="n">
         <v>4.81146</v>
       </c>
-      <c r="K110" s="3" t="n">
+      <c r="K110" s="2" t="n">
         <v>4.07802</v>
       </c>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
+      <c r="Q110" s="2" t="n"/>
+      <c r="R110" s="2" t="n"/>
+      <c r="S110" s="2" t="n"/>
+      <c r="T110" s="2" t="n"/>
+      <c r="U110" s="2" t="n"/>
+      <c r="X110" s="2" t="n"/>
+      <c r="Y110" s="2" t="n"/>
+      <c r="Z110" s="2" t="n"/>
+      <c r="AA110" s="2" t="n"/>
+      <c r="AB110" s="2" t="n"/>
+      <c r="AC110" s="2" t="n"/>
+      <c r="AD110" s="2" t="n"/>
+      <c r="AE110" s="2" t="n"/>
     </row>
     <row r="111">
-      <c r="E111" s="3" t="n">
+      <c r="E111" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F111" s="3" t="n">
+      <c r="F111" s="2" t="n">
         <v>4.86752</v>
       </c>
-      <c r="G111" s="3" t="n">
+      <c r="G111" s="2" t="n">
         <v>3.08449</v>
       </c>
-      <c r="H111" s="3" t="n">
+      <c r="H111" s="2" t="n">
         <v>3.85941</v>
       </c>
-      <c r="I111" s="3" t="n">
+      <c r="I111" s="2" t="n">
         <v>3.97265</v>
       </c>
-      <c r="J111" s="3" t="n">
+      <c r="J111" s="2" t="n">
         <v>4.53676</v>
       </c>
-      <c r="K111" s="3" t="n">
+      <c r="K111" s="2" t="n">
         <v>4.13842</v>
       </c>
+      <c r="N111" s="2" t="n"/>
+      <c r="O111" s="2" t="n"/>
+      <c r="P111" s="2" t="n"/>
+      <c r="Q111" s="2" t="n"/>
+      <c r="R111" s="2" t="n"/>
+      <c r="S111" s="2" t="n"/>
+      <c r="T111" s="2" t="n"/>
+      <c r="U111" s="2" t="n"/>
+      <c r="X111" s="2" t="n"/>
+      <c r="Y111" s="2" t="n"/>
+      <c r="Z111" s="2" t="n"/>
+      <c r="AA111" s="2" t="n"/>
+      <c r="AB111" s="2" t="n"/>
+      <c r="AC111" s="2" t="n"/>
+      <c r="AD111" s="2" t="n"/>
+      <c r="AE111" s="2" t="n"/>
     </row>
     <row r="112">
-      <c r="E112" s="3" t="n">
+      <c r="E112" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F112" s="3" t="n">
+      <c r="F112" s="2" t="n">
         <v>5.215</v>
       </c>
-      <c r="G112" s="3" t="n">
+      <c r="G112" s="2" t="n">
         <v>3.02471</v>
       </c>
-      <c r="H112" s="3" t="n">
+      <c r="H112" s="2" t="n">
         <v>3.89843</v>
       </c>
-      <c r="I112" s="3" t="n">
+      <c r="I112" s="2" t="n">
         <v>4.05517</v>
       </c>
-      <c r="J112" s="3" t="n">
+      <c r="J112" s="2" t="n">
         <v>4.30283</v>
       </c>
-      <c r="K112" s="3" t="n">
+      <c r="K112" s="2" t="n">
         <v>4.20544</v>
       </c>
+      <c r="N112" s="2" t="n"/>
+      <c r="O112" s="2" t="n"/>
+      <c r="P112" s="2" t="n"/>
+      <c r="Q112" s="2" t="n"/>
+      <c r="R112" s="2" t="n"/>
+      <c r="S112" s="2" t="n"/>
+      <c r="T112" s="2" t="n"/>
+      <c r="U112" s="2" t="n"/>
+      <c r="X112" s="2" t="n"/>
+      <c r="Y112" s="2" t="n"/>
+      <c r="Z112" s="2" t="n"/>
+      <c r="AA112" s="2" t="n"/>
+      <c r="AB112" s="2" t="n"/>
+      <c r="AC112" s="2" t="n"/>
+      <c r="AD112" s="2" t="n"/>
+      <c r="AE112" s="2" t="n"/>
     </row>
     <row r="113">
-      <c r="E113" s="3" t="n">
+      <c r="E113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F113" s="3" t="n">
+      <c r="F113" s="2" t="n">
         <v>5.22394</v>
       </c>
-      <c r="G113" s="3" t="n">
+      <c r="G113" s="2" t="n">
         <v>2.91395</v>
       </c>
-      <c r="H113" s="3" t="n">
+      <c r="H113" s="2" t="n">
         <v>3.82372</v>
       </c>
-      <c r="I113" s="3" t="n">
+      <c r="I113" s="2" t="n">
         <v>3.90048</v>
       </c>
-      <c r="J113" s="3" t="n">
+      <c r="J113" s="2" t="n">
         <v>4.22289</v>
       </c>
-      <c r="K113" s="3" t="n">
+      <c r="K113" s="2" t="n">
         <v>4.14564</v>
       </c>
+      <c r="N113" s="2" t="n"/>
+      <c r="O113" s="2" t="n"/>
+      <c r="P113" s="2" t="n"/>
+      <c r="Q113" s="2" t="n"/>
+      <c r="R113" s="2" t="n"/>
+      <c r="S113" s="2" t="n"/>
+      <c r="T113" s="2" t="n"/>
+      <c r="U113" s="2" t="n"/>
+      <c r="X113" s="2" t="n"/>
+      <c r="Y113" s="2" t="n"/>
+      <c r="Z113" s="2" t="n"/>
+      <c r="AA113" s="2" t="n"/>
+      <c r="AB113" s="2" t="n"/>
+      <c r="AC113" s="2" t="n"/>
+      <c r="AD113" s="2" t="n"/>
+      <c r="AE113" s="2" t="n"/>
     </row>
     <row r="114">
-      <c r="E114" s="3" t="n">
+      <c r="E114" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F114" s="3" t="n">
+      <c r="F114" s="2" t="n">
         <v>4.88615</v>
       </c>
-      <c r="G114" s="3" t="n">
+      <c r="G114" s="2" t="n">
         <v>2.68523</v>
       </c>
-      <c r="H114" s="3" t="n">
+      <c r="H114" s="2" t="n">
         <v>3.5826</v>
       </c>
-      <c r="I114" s="3" t="n">
+      <c r="I114" s="2" t="n">
         <v>3.65424</v>
       </c>
-      <c r="J114" s="3" t="n">
+      <c r="J114" s="2" t="n">
         <v>4.11785</v>
       </c>
-      <c r="K114" s="3" t="n">
+      <c r="K114" s="2" t="n">
         <v>3.67876</v>
       </c>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="2" t="n"/>
+      <c r="Q114" s="2" t="n"/>
+      <c r="R114" s="2" t="n"/>
+      <c r="S114" s="2" t="n"/>
+      <c r="T114" s="2" t="n"/>
+      <c r="U114" s="2" t="n"/>
+      <c r="X114" s="2" t="n"/>
+      <c r="Y114" s="2" t="n"/>
+      <c r="Z114" s="2" t="n"/>
+      <c r="AA114" s="2" t="n"/>
+      <c r="AB114" s="2" t="n"/>
+      <c r="AC114" s="2" t="n"/>
+      <c r="AD114" s="2" t="n"/>
+      <c r="AE114" s="2" t="n"/>
     </row>
     <row r="115">
-      <c r="E115" s="3" t="n">
+      <c r="E115" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F115" s="3" t="n">
+      <c r="F115" s="2" t="n">
         <v>4.45347</v>
       </c>
-      <c r="G115" s="3" t="n">
+      <c r="G115" s="2" t="n">
         <v>2.40058</v>
       </c>
-      <c r="H115" s="3" t="n">
+      <c r="H115" s="2" t="n">
         <v>3.18861</v>
       </c>
-      <c r="I115" s="3" t="n">
+      <c r="I115" s="2" t="n">
         <v>3.46411</v>
       </c>
-      <c r="J115" s="3" t="n">
+      <c r="J115" s="2" t="n">
         <v>4.0787</v>
       </c>
-      <c r="K115" s="3" t="n">
+      <c r="K115" s="2" t="n">
         <v>3.13743</v>
       </c>
+      <c r="N115" s="2" t="n"/>
+      <c r="O115" s="2" t="n"/>
+      <c r="P115" s="2" t="n"/>
+      <c r="Q115" s="2" t="n"/>
+      <c r="R115" s="2" t="n"/>
+      <c r="S115" s="2" t="n"/>
+      <c r="T115" s="2" t="n"/>
+      <c r="U115" s="2" t="n"/>
+      <c r="X115" s="2" t="n"/>
+      <c r="Y115" s="2" t="n"/>
+      <c r="Z115" s="2" t="n"/>
+      <c r="AA115" s="2" t="n"/>
+      <c r="AB115" s="2" t="n"/>
+      <c r="AC115" s="2" t="n"/>
+      <c r="AD115" s="2" t="n"/>
+      <c r="AE115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="N116" s="2" t="n"/>
+      <c r="O116" s="2" t="n"/>
+      <c r="P116" s="2" t="n"/>
+      <c r="Q116" s="2" t="n"/>
+      <c r="R116" s="2" t="n"/>
+      <c r="S116" s="2" t="n"/>
+      <c r="T116" s="2" t="n"/>
+      <c r="U116" s="2" t="n"/>
+      <c r="X116" s="2" t="n"/>
+      <c r="Y116" s="2" t="n"/>
+      <c r="Z116" s="2" t="n"/>
+      <c r="AA116" s="2" t="n"/>
+      <c r="AB116" s="2" t="n"/>
+      <c r="AC116" s="2" t="n"/>
+      <c r="AD116" s="2" t="n"/>
+      <c r="AE116" s="2" t="n"/>
     </row>
     <row r="117">
-      <c r="D117" s="8" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>DIA-PreResNet-56</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>MIFGSM</t>
         </is>
       </c>
-      <c r="F117" s="3" t="n">
+      <c r="F117" s="2" t="n">
         <v>3.25545</v>
       </c>
-      <c r="G117" s="3" t="n">
+      <c r="G117" s="2" t="n">
         <v>2.40469</v>
       </c>
-      <c r="H117" s="3" t="n">
+      <c r="H117" s="2" t="n">
         <v>2.30561</v>
       </c>
-      <c r="I117" s="3" t="n">
+      <c r="I117" s="2" t="n">
         <v>2.59116</v>
       </c>
-      <c r="J117" s="3" t="n">
+      <c r="J117" s="2" t="n">
         <v>2.06655</v>
       </c>
-      <c r="K117" s="3" t="n">
+      <c r="K117" s="2" t="n">
         <v>7.09179</v>
       </c>
+      <c r="N117" s="2" t="n"/>
+      <c r="O117" s="2" t="n"/>
+      <c r="P117" s="2" t="n"/>
+      <c r="Q117" s="2" t="n"/>
+      <c r="R117" s="2" t="n"/>
+      <c r="S117" s="2" t="n"/>
+      <c r="T117" s="2" t="n"/>
+      <c r="U117" s="2" t="n"/>
+      <c r="X117" s="2" t="n"/>
+      <c r="Y117" s="2" t="n"/>
+      <c r="Z117" s="2" t="n"/>
+      <c r="AA117" s="2" t="n"/>
+      <c r="AB117" s="2" t="n"/>
+      <c r="AC117" s="2" t="n"/>
+      <c r="AD117" s="2" t="n"/>
+      <c r="AE117" s="2" t="n"/>
     </row>
     <row r="118">
-      <c r="E118" s="3" t="n">
+      <c r="E118" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F118" s="3" t="n">
+      <c r="F118" s="2" t="n">
         <v>3.33047</v>
       </c>
-      <c r="G118" s="3" t="n">
+      <c r="G118" s="2" t="n">
         <v>2.61097</v>
       </c>
-      <c r="H118" s="3" t="n">
+      <c r="H118" s="2" t="n">
         <v>2.66209</v>
       </c>
-      <c r="I118" s="3" t="n">
+      <c r="I118" s="2" t="n">
         <v>2.92741</v>
       </c>
-      <c r="J118" s="3" t="n">
+      <c r="J118" s="2" t="n">
         <v>2.25123</v>
       </c>
-      <c r="K118" s="3" t="n">
+      <c r="K118" s="2" t="n">
         <v>6.73145</v>
       </c>
+      <c r="N118" s="2" t="n"/>
+      <c r="O118" s="2" t="n"/>
+      <c r="P118" s="2" t="n"/>
+      <c r="Q118" s="2" t="n"/>
+      <c r="R118" s="2" t="n"/>
+      <c r="S118" s="2" t="n"/>
+      <c r="T118" s="2" t="n"/>
+      <c r="U118" s="2" t="n"/>
+      <c r="X118" s="2" t="n"/>
+      <c r="Y118" s="2" t="n"/>
+      <c r="Z118" s="2" t="n"/>
+      <c r="AA118" s="2" t="n"/>
+      <c r="AB118" s="2" t="n"/>
+      <c r="AC118" s="2" t="n"/>
+      <c r="AD118" s="2" t="n"/>
+      <c r="AE118" s="2" t="n"/>
     </row>
     <row r="119">
-      <c r="E119" s="3" t="n">
+      <c r="E119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="3" t="n">
+      <c r="F119" s="2" t="n">
         <v>3.50584</v>
       </c>
-      <c r="G119" s="3" t="n">
+      <c r="G119" s="2" t="n">
         <v>2.63476</v>
       </c>
-      <c r="H119" s="3" t="n">
+      <c r="H119" s="2" t="n">
         <v>2.69106</v>
       </c>
-      <c r="I119" s="3" t="n">
+      <c r="I119" s="2" t="n">
         <v>2.90856</v>
       </c>
-      <c r="J119" s="3" t="n">
+      <c r="J119" s="2" t="n">
         <v>2.32654</v>
       </c>
-      <c r="K119" s="3" t="n">
+      <c r="K119" s="2" t="n">
         <v>6.02728</v>
       </c>
+      <c r="N119" s="2" t="n"/>
+      <c r="O119" s="2" t="n"/>
+      <c r="P119" s="2" t="n"/>
+      <c r="Q119" s="2" t="n"/>
+      <c r="R119" s="2" t="n"/>
+      <c r="S119" s="2" t="n"/>
+      <c r="T119" s="2" t="n"/>
+      <c r="U119" s="2" t="n"/>
+      <c r="X119" s="2" t="n"/>
+      <c r="Y119" s="2" t="n"/>
+      <c r="Z119" s="2" t="n"/>
+      <c r="AA119" s="2" t="n"/>
+      <c r="AB119" s="2" t="n"/>
+      <c r="AC119" s="2" t="n"/>
+      <c r="AD119" s="2" t="n"/>
+      <c r="AE119" s="2" t="n"/>
     </row>
     <row r="120">
-      <c r="E120" s="3" t="n">
+      <c r="E120" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F120" s="3" t="n">
+      <c r="F120" s="2" t="n">
         <v>4.54736</v>
       </c>
-      <c r="G120" s="3" t="n">
+      <c r="G120" s="2" t="n">
         <v>3.05303</v>
       </c>
-      <c r="H120" s="3" t="n">
+      <c r="H120" s="2" t="n">
         <v>3.42126</v>
       </c>
-      <c r="I120" s="3" t="n">
+      <c r="I120" s="2" t="n">
         <v>3.5237</v>
       </c>
-      <c r="J120" s="3" t="n">
+      <c r="J120" s="2" t="n">
         <v>2.72446</v>
       </c>
-      <c r="K120" s="3" t="n">
+      <c r="K120" s="2" t="n">
         <v>6.30271</v>
       </c>
+      <c r="N120" s="2" t="n"/>
+      <c r="O120" s="2" t="n"/>
+      <c r="P120" s="2" t="n"/>
+      <c r="Q120" s="2" t="n"/>
+      <c r="R120" s="2" t="n"/>
+      <c r="S120" s="2" t="n"/>
+      <c r="T120" s="2" t="n"/>
+      <c r="U120" s="2" t="n"/>
+      <c r="X120" s="2" t="n"/>
+      <c r="Y120" s="2" t="n"/>
+      <c r="Z120" s="2" t="n"/>
+      <c r="AA120" s="2" t="n"/>
+      <c r="AB120" s="2" t="n"/>
+      <c r="AC120" s="2" t="n"/>
+      <c r="AD120" s="2" t="n"/>
+      <c r="AE120" s="2" t="n"/>
     </row>
     <row r="121">
-      <c r="E121" s="3" t="n">
+      <c r="E121" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F121" s="3" t="n">
+      <c r="F121" s="2" t="n">
         <v>5.00058</v>
       </c>
-      <c r="G121" s="3" t="n">
+      <c r="G121" s="2" t="n">
         <v>3.17491</v>
       </c>
-      <c r="H121" s="3" t="n">
+      <c r="H121" s="2" t="n">
         <v>3.91396</v>
       </c>
-      <c r="I121" s="3" t="n">
+      <c r="I121" s="2" t="n">
         <v>3.87685</v>
       </c>
-      <c r="J121" s="3" t="n">
+      <c r="J121" s="2" t="n">
         <v>2.86181</v>
       </c>
-      <c r="K121" s="3" t="n">
+      <c r="K121" s="2" t="n">
         <v>6.39424</v>
       </c>
+      <c r="N121" s="2" t="n"/>
+      <c r="O121" s="2" t="n"/>
+      <c r="P121" s="2" t="n"/>
+      <c r="Q121" s="2" t="n"/>
+      <c r="R121" s="2" t="n"/>
+      <c r="S121" s="2" t="n"/>
+      <c r="T121" s="2" t="n"/>
+      <c r="U121" s="2" t="n"/>
+      <c r="X121" s="2" t="n"/>
+      <c r="Y121" s="2" t="n"/>
+      <c r="Z121" s="2" t="n"/>
+      <c r="AA121" s="2" t="n"/>
+      <c r="AB121" s="2" t="n"/>
+      <c r="AC121" s="2" t="n"/>
+      <c r="AD121" s="2" t="n"/>
+      <c r="AE121" s="2" t="n"/>
     </row>
     <row r="122">
-      <c r="E122" s="3" t="n">
+      <c r="E122" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="F122" s="3" t="n">
+      <c r="F122" s="2" t="n">
         <v>5.40266</v>
       </c>
-      <c r="G122" s="3" t="n">
+      <c r="G122" s="2" t="n">
         <v>3.1888</v>
       </c>
-      <c r="H122" s="3" t="n">
+      <c r="H122" s="2" t="n">
         <v>4.0229</v>
       </c>
-      <c r="I122" s="3" t="n">
+      <c r="I122" s="2" t="n">
         <v>3.90637</v>
       </c>
-      <c r="J122" s="3" t="n">
+      <c r="J122" s="2" t="n">
         <v>2.93938</v>
       </c>
-      <c r="K122" s="3" t="n">
+      <c r="K122" s="2" t="n">
         <v>6.43327</v>
       </c>
+      <c r="N122" s="2" t="n"/>
+      <c r="O122" s="2" t="n"/>
+      <c r="P122" s="2" t="n"/>
+      <c r="Q122" s="2" t="n"/>
+      <c r="R122" s="2" t="n"/>
+      <c r="S122" s="2" t="n"/>
+      <c r="T122" s="2" t="n"/>
+      <c r="U122" s="2" t="n"/>
+      <c r="X122" s="2" t="n"/>
+      <c r="Y122" s="2" t="n"/>
+      <c r="Z122" s="2" t="n"/>
+      <c r="AA122" s="2" t="n"/>
+      <c r="AB122" s="2" t="n"/>
+      <c r="AC122" s="2" t="n"/>
+      <c r="AD122" s="2" t="n"/>
+      <c r="AE122" s="2" t="n"/>
     </row>
     <row r="123">
-      <c r="E123" s="3" t="n">
+      <c r="E123" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F123" s="3" t="n">
+      <c r="F123" s="2" t="n">
         <v>5.32115</v>
       </c>
-      <c r="G123" s="3" t="n">
+      <c r="G123" s="2" t="n">
         <v>3.01057</v>
       </c>
-      <c r="H123" s="3" t="n">
+      <c r="H123" s="2" t="n">
         <v>4.00404</v>
       </c>
-      <c r="I123" s="3" t="n">
+      <c r="I123" s="2" t="n">
         <v>3.89982</v>
       </c>
-      <c r="J123" s="3" t="n">
+      <c r="J123" s="2" t="n">
         <v>2.7541</v>
       </c>
-      <c r="K123" s="3" t="n">
+      <c r="K123" s="2" t="n">
         <v>6.51448</v>
       </c>
+      <c r="N123" s="2" t="n"/>
+      <c r="O123" s="2" t="n"/>
+      <c r="P123" s="2" t="n"/>
+      <c r="Q123" s="2" t="n"/>
+      <c r="R123" s="2" t="n"/>
+      <c r="S123" s="2" t="n"/>
+      <c r="T123" s="2" t="n"/>
+      <c r="U123" s="2" t="n"/>
+      <c r="X123" s="2" t="n"/>
+      <c r="Y123" s="2" t="n"/>
+      <c r="Z123" s="2" t="n"/>
+      <c r="AA123" s="2" t="n"/>
+      <c r="AB123" s="2" t="n"/>
+      <c r="AC123" s="2" t="n"/>
+      <c r="AD123" s="2" t="n"/>
+      <c r="AE123" s="2" t="n"/>
     </row>
     <row r="124">
-      <c r="E124" s="3" t="n">
+      <c r="E124" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F124" s="3" t="n">
+      <c r="F124" s="2" t="n">
         <v>5.06484</v>
       </c>
-      <c r="G124" s="3" t="n">
+      <c r="G124" s="2" t="n">
         <v>2.7978</v>
       </c>
-      <c r="H124" s="3" t="n">
+      <c r="H124" s="2" t="n">
         <v>3.76481</v>
       </c>
-      <c r="I124" s="3" t="n">
+      <c r="I124" s="2" t="n">
         <v>3.76457</v>
       </c>
-      <c r="J124" s="3" t="n">
+      <c r="J124" s="2" t="n">
         <v>2.555</v>
       </c>
-      <c r="K124" s="3" t="n">
+      <c r="K124" s="2" t="n">
         <v>6.57915</v>
       </c>
+      <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
+      <c r="P124" s="2" t="n"/>
+      <c r="Q124" s="2" t="n"/>
+      <c r="R124" s="2" t="n"/>
+      <c r="S124" s="2" t="n"/>
+      <c r="T124" s="2" t="n"/>
+      <c r="U124" s="2" t="n"/>
+      <c r="X124" s="2" t="n"/>
+      <c r="Y124" s="2" t="n"/>
+      <c r="Z124" s="2" t="n"/>
+      <c r="AA124" s="2" t="n"/>
+      <c r="AB124" s="2" t="n"/>
+      <c r="AC124" s="2" t="n"/>
+      <c r="AD124" s="2" t="n"/>
+      <c r="AE124" s="2" t="n"/>
     </row>
     <row r="125">
-      <c r="E125" s="3" t="n">
+      <c r="E125" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F125" s="3" t="n">
+      <c r="F125" s="2" t="n">
         <v>4.53192</v>
       </c>
-      <c r="G125" s="3" t="n">
+      <c r="G125" s="2" t="n">
         <v>2.45848</v>
       </c>
-      <c r="H125" s="3" t="n">
+      <c r="H125" s="2" t="n">
         <v>3.39727</v>
       </c>
-      <c r="I125" s="3" t="n">
+      <c r="I125" s="2" t="n">
         <v>3.45727</v>
       </c>
-      <c r="J125" s="3" t="n">
+      <c r="J125" s="2" t="n">
         <v>2.27774</v>
       </c>
-      <c r="K125" s="3" t="n">
+      <c r="K125" s="2" t="n">
         <v>6.45521</v>
       </c>
+      <c r="N125" s="2" t="n"/>
+      <c r="O125" s="2" t="n"/>
+      <c r="P125" s="2" t="n"/>
+      <c r="Q125" s="2" t="n"/>
+      <c r="R125" s="2" t="n"/>
+      <c r="S125" s="2" t="n"/>
+      <c r="T125" s="2" t="n"/>
+      <c r="U125" s="2" t="n"/>
+      <c r="X125" s="2" t="n"/>
+      <c r="Y125" s="2" t="n"/>
+      <c r="Z125" s="2" t="n"/>
+      <c r="AA125" s="2" t="n"/>
+      <c r="AB125" s="2" t="n"/>
+      <c r="AC125" s="2" t="n"/>
+      <c r="AD125" s="2" t="n"/>
+      <c r="AE125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="N126" s="2" t="n"/>
+      <c r="O126" s="2" t="n"/>
+      <c r="P126" s="2" t="n"/>
+      <c r="Q126" s="2" t="n"/>
+      <c r="R126" s="2" t="n"/>
+      <c r="S126" s="2" t="n"/>
+      <c r="T126" s="2" t="n"/>
+      <c r="U126" s="2" t="n"/>
+      <c r="X126" s="2" t="n"/>
+      <c r="Y126" s="2" t="n"/>
+      <c r="Z126" s="2" t="n"/>
+      <c r="AA126" s="2" t="n"/>
+      <c r="AB126" s="2" t="n"/>
+      <c r="AC126" s="2" t="n"/>
+      <c r="AD126" s="2" t="n"/>
+      <c r="AE126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="N127" s="2" t="n"/>
+      <c r="O127" s="2" t="n"/>
+      <c r="P127" s="2" t="n"/>
+      <c r="Q127" s="2" t="n"/>
+      <c r="R127" s="2" t="n"/>
+      <c r="S127" s="2" t="n"/>
+      <c r="T127" s="2" t="n"/>
+      <c r="U127" s="2" t="n"/>
+      <c r="X127" s="2" t="n"/>
+      <c r="Y127" s="2" t="n"/>
+      <c r="Z127" s="2" t="n"/>
+      <c r="AA127" s="2" t="n"/>
+      <c r="AB127" s="2" t="n"/>
+      <c r="AC127" s="2" t="n"/>
+      <c r="AD127" s="2" t="n"/>
+      <c r="AE127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="n"/>
+      <c r="P128" s="2" t="n"/>
+      <c r="Q128" s="2" t="n"/>
+      <c r="R128" s="2" t="n"/>
+      <c r="S128" s="2" t="n"/>
+      <c r="T128" s="2" t="n"/>
+      <c r="U128" s="2" t="n"/>
+      <c r="X128" s="2" t="n"/>
+      <c r="Y128" s="2" t="n"/>
+      <c r="Z128" s="2" t="n"/>
+      <c r="AA128" s="2" t="n"/>
+      <c r="AB128" s="2" t="n"/>
+      <c r="AC128" s="2" t="n"/>
+      <c r="AD128" s="2" t="n"/>
+      <c r="AE128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="N129" s="2" t="n"/>
+      <c r="O129" s="2" t="n"/>
+      <c r="P129" s="2" t="n"/>
+      <c r="Q129" s="2" t="n"/>
+      <c r="R129" s="2" t="n"/>
+      <c r="S129" s="2" t="n"/>
+      <c r="T129" s="2" t="n"/>
+      <c r="U129" s="2" t="n"/>
+      <c r="X129" s="2" t="n"/>
+      <c r="Y129" s="2" t="n"/>
+      <c r="Z129" s="2" t="n"/>
+      <c r="AA129" s="2" t="n"/>
+      <c r="AB129" s="2" t="n"/>
+      <c r="AC129" s="2" t="n"/>
+      <c r="AD129" s="2" t="n"/>
+      <c r="AE129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="N130" s="2" t="n"/>
+      <c r="O130" s="2" t="n"/>
+      <c r="P130" s="2" t="n"/>
+      <c r="Q130" s="2" t="n"/>
+      <c r="R130" s="2" t="n"/>
+      <c r="S130" s="2" t="n"/>
+      <c r="T130" s="2" t="n"/>
+      <c r="U130" s="2" t="n"/>
+      <c r="X130" s="2" t="n"/>
+      <c r="Y130" s="2" t="n"/>
+      <c r="Z130" s="2" t="n"/>
+      <c r="AA130" s="2" t="n"/>
+      <c r="AB130" s="2" t="n"/>
+      <c r="AC130" s="2" t="n"/>
+      <c r="AD130" s="2" t="n"/>
+      <c r="AE130" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="36">
+    <mergeCell ref="X83:X85"/>
+    <mergeCell ref="N67:N71"/>
+    <mergeCell ref="N10:N14"/>
+    <mergeCell ref="N73:N77"/>
+    <mergeCell ref="X4:X6"/>
+    <mergeCell ref="X20:X22"/>
+    <mergeCell ref="D107:D115"/>
+    <mergeCell ref="D87:D95"/>
+    <mergeCell ref="N28:N32"/>
+    <mergeCell ref="X79:X81"/>
+    <mergeCell ref="D97:D105"/>
+    <mergeCell ref="X75:X77"/>
+    <mergeCell ref="D4:D12"/>
+    <mergeCell ref="N34:N38"/>
+    <mergeCell ref="X12:X14"/>
+    <mergeCell ref="X8:X10"/>
+    <mergeCell ref="D24:D32"/>
+    <mergeCell ref="X71:X73"/>
+    <mergeCell ref="X67:X69"/>
     <mergeCell ref="D14:D22"/>
+    <mergeCell ref="D67:D75"/>
+    <mergeCell ref="N79:N83"/>
+    <mergeCell ref="N4:N8"/>
+    <mergeCell ref="D117:D125"/>
+    <mergeCell ref="N91:N95"/>
+    <mergeCell ref="N85:N89"/>
+    <mergeCell ref="N16:N20"/>
+    <mergeCell ref="X16:X18"/>
+    <mergeCell ref="D54:D62"/>
+    <mergeCell ref="D34:D42"/>
+    <mergeCell ref="N97:N101"/>
+    <mergeCell ref="N22:N26"/>
     <mergeCell ref="D44:D52"/>
-    <mergeCell ref="D4:D12"/>
-    <mergeCell ref="D67:D75"/>
+    <mergeCell ref="X87:X89"/>
+    <mergeCell ref="X24:X26"/>
     <mergeCell ref="D77:D85"/>
-    <mergeCell ref="D117:D125"/>
-    <mergeCell ref="D107:D115"/>
-    <mergeCell ref="D34:D42"/>
-    <mergeCell ref="D54:D62"/>
-    <mergeCell ref="D87:D95"/>
-    <mergeCell ref="D24:D32"/>
-    <mergeCell ref="D97:D105"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
